--- a/src/attributions/attributions_saliency_traj_182.xlsx
+++ b/src/attributions/attributions_saliency_traj_182.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG3"/>
+  <dimension ref="A1:GG16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,1139 +999,8536 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4.144526428717654e-06</v>
+        <v>0.01064122840762138</v>
       </c>
       <c r="B2" t="n">
-        <v>4.932362207910046e-05</v>
+        <v>0.0751301497220993</v>
       </c>
       <c r="C2" t="n">
-        <v>9.690566002973355e-06</v>
+        <v>0.0964106023311615</v>
       </c>
       <c r="D2" t="n">
-        <v>8.084299770416692e-05</v>
+        <v>0.175305187702179</v>
       </c>
       <c r="E2" t="n">
-        <v>1.14667127490975e-05</v>
+        <v>0.1137134060263634</v>
       </c>
       <c r="F2" t="n">
-        <v>1.34490646814811e-05</v>
+        <v>0.04088070243597031</v>
       </c>
       <c r="G2" t="n">
-        <v>1.630315637157764e-05</v>
+        <v>0.02464236877858639</v>
       </c>
       <c r="H2" t="n">
-        <v>1.555245944473427e-05</v>
+        <v>0.01834327727556229</v>
       </c>
       <c r="I2" t="n">
-        <v>2.269688593514729e-06</v>
+        <v>0.04244937747716904</v>
       </c>
       <c r="J2" t="n">
-        <v>1.328576399828307e-05</v>
+        <v>0.01169674471020699</v>
       </c>
       <c r="K2" t="n">
-        <v>4.921060826745816e-05</v>
+        <v>0.06651866436004639</v>
       </c>
       <c r="L2" t="n">
-        <v>1.723319883240038e-06</v>
+        <v>0.08248421549797058</v>
       </c>
       <c r="M2" t="n">
-        <v>7.7106109529268e-05</v>
+        <v>0.1428426206111908</v>
       </c>
       <c r="N2" t="n">
-        <v>2.392959686403628e-06</v>
+        <v>0.1281919330358505</v>
       </c>
       <c r="O2" t="n">
-        <v>4.64025761175435e-05</v>
+        <v>0.02340479008853436</v>
       </c>
       <c r="P2" t="n">
-        <v>1.019044248096179e-05</v>
+        <v>0.01203957200050354</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.295576268807054e-05</v>
+        <v>0.05495712906122208</v>
       </c>
       <c r="R2" t="n">
-        <v>2.306529313500505e-05</v>
+        <v>0.03728709369897842</v>
       </c>
       <c r="S2" t="n">
-        <v>1.288300973101286e-05</v>
+        <v>0.01708346791565418</v>
       </c>
       <c r="T2" t="n">
-        <v>1.611947482160758e-05</v>
+        <v>0.02330291271209717</v>
       </c>
       <c r="U2" t="n">
-        <v>4.559598892228678e-06</v>
+        <v>0.007025778293609619</v>
       </c>
       <c r="V2" t="n">
-        <v>3.037357600987889e-07</v>
+        <v>0.07183162868022919</v>
       </c>
       <c r="W2" t="n">
-        <v>1.60008821694646e-05</v>
+        <v>0.0001214428339153528</v>
       </c>
       <c r="X2" t="n">
-        <v>1.899886774481274e-05</v>
+        <v>0.07864397764205933</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.897942638606764e-06</v>
+        <v>0.04295278340578079</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.105013143387623e-05</v>
+        <v>0.003620577044785023</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.797705408534966e-06</v>
+        <v>0.09173480421304703</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.087757275148761e-05</v>
+        <v>0.04589793831110001</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.9020135368919e-05</v>
+        <v>0.04322513565421104</v>
       </c>
       <c r="AD2" t="n">
-        <v>7.663576980121434e-06</v>
+        <v>0.03235544636845589</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.384652114211349e-05</v>
+        <v>0.01120725460350513</v>
       </c>
       <c r="AF2" t="n">
-        <v>3.529350578901358e-05</v>
+        <v>0.01352228969335556</v>
       </c>
       <c r="AG2" t="n">
-        <v>8.296691703435499e-06</v>
+        <v>0.001775016309693456</v>
       </c>
       <c r="AH2" t="n">
-        <v>6.521265277115162e-06</v>
+        <v>0.03758153319358826</v>
       </c>
       <c r="AI2" t="n">
-        <v>4.050702955282759e-06</v>
+        <v>0.0432359091937542</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.232795966643607e-05</v>
+        <v>0.02646225318312645</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.459560007788241e-05</v>
+        <v>0.0252342913299799</v>
       </c>
       <c r="AL2" t="n">
-        <v>3.016890514118131e-05</v>
+        <v>0.05527609586715698</v>
       </c>
       <c r="AM2" t="n">
-        <v>2.899922037613578e-06</v>
+        <v>0.01568895950913429</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.264731963601662e-05</v>
+        <v>0.003401681780815125</v>
       </c>
       <c r="AO2" t="n">
-        <v>4.924433483211033e-07</v>
+        <v>0.09890972822904587</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.939886937587289e-06</v>
+        <v>0.006688717752695084</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.315225851314608e-06</v>
+        <v>0.01769581995904446</v>
       </c>
       <c r="AR2" t="n">
-        <v>8.411585440626368e-06</v>
+        <v>0.02106387168169022</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.770402367488714e-06</v>
+        <v>0.03937387466430664</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.51209505929728e-05</v>
+        <v>0.01622334308922291</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.706058719719294e-05</v>
+        <v>0.1127626821398735</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.839422793636913e-06</v>
+        <v>0.01969105750322342</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.048286064062268e-05</v>
+        <v>0.02270013839006424</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.99222267838195e-05</v>
+        <v>0.03223183378577232</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.282660923607182e-05</v>
+        <v>0.02080511674284935</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.237140713783447e-05</v>
+        <v>0.02727913670241833</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.224663037646678e-08</v>
+        <v>0.004216405563056469</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.792065167042892e-06</v>
+        <v>0.0694485530257225</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.683611455722712e-06</v>
+        <v>0.01290282607078552</v>
       </c>
       <c r="BD2" t="n">
-        <v>2.178236900363117e-05</v>
+        <v>0.1277766227722168</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.664307991537498e-06</v>
+        <v>0.07998613268136978</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.769484126474708e-05</v>
+        <v>0.09833889454603195</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.879785824916326e-06</v>
+        <v>0.1102179065346718</v>
       </c>
       <c r="BH2" t="n">
-        <v>6.660578492301283e-06</v>
+        <v>0.002916290424764156</v>
       </c>
       <c r="BI2" t="n">
-        <v>4.058289960084949e-06</v>
+        <v>0.01552732661366463</v>
       </c>
       <c r="BJ2" t="n">
-        <v>3.220113967472571e-06</v>
+        <v>0.01863465458154678</v>
       </c>
       <c r="BK2" t="n">
-        <v>4.022797838842962e-06</v>
+        <v>0.03552909195423126</v>
       </c>
       <c r="BL2" t="n">
-        <v>2.532953658374026e-05</v>
+        <v>0.0005626482889056206</v>
       </c>
       <c r="BM2" t="n">
-        <v>3.248593930038624e-05</v>
+        <v>0.05663812905550003</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.975170675905247e-07</v>
+        <v>0.006456222385168076</v>
       </c>
       <c r="BO2" t="n">
-        <v>7.81621019996237e-06</v>
+        <v>0.0759071558713913</v>
       </c>
       <c r="BP2" t="n">
-        <v>6.226326831892948e-07</v>
+        <v>0.05790338665246964</v>
       </c>
       <c r="BQ2" t="n">
-        <v>9.244369039151934e-07</v>
+        <v>0.006943365558981895</v>
       </c>
       <c r="BR2" t="n">
-        <v>3.909067345375661e-06</v>
+        <v>0.06175816431641579</v>
       </c>
       <c r="BS2" t="n">
-        <v>2.533625320211286e-06</v>
+        <v>0.0007428531534969807</v>
       </c>
       <c r="BT2" t="n">
-        <v>7.524651209678268e-06</v>
+        <v>0.001100815599784255</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.947992132045329e-05</v>
+        <v>0.0343838594853878</v>
       </c>
       <c r="BV2" t="n">
-        <v>1.619713293621317e-05</v>
+        <v>0.1100063547492027</v>
       </c>
       <c r="BW2" t="n">
-        <v>4.336457095632795e-07</v>
+        <v>0.0125716608017683</v>
       </c>
       <c r="BX2" t="n">
-        <v>1.371795769955497e-05</v>
+        <v>0.08618324995040894</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.285807957174256e-05</v>
+        <v>0.05865193158388138</v>
       </c>
       <c r="BZ2" t="n">
-        <v>6.754827154509258e-06</v>
+        <v>0.04954404756426811</v>
       </c>
       <c r="CA2" t="n">
-        <v>7.83234372647712e-06</v>
+        <v>0.05636463686823845</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.108485882170498e-06</v>
+        <v>0.02936220727860928</v>
       </c>
       <c r="CC2" t="n">
-        <v>1.239958237420069e-05</v>
+        <v>0.09236525744199753</v>
       </c>
       <c r="CD2" t="n">
-        <v>1.314334622293245e-05</v>
+        <v>0.0009050192311406136</v>
       </c>
       <c r="CE2" t="n">
-        <v>3.416211484363885e-06</v>
+        <v>0.04773516580462456</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.111685262207175e-06</v>
+        <v>0.02819366380572319</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.015551035583485e-05</v>
+        <v>0.05505295097827911</v>
       </c>
       <c r="CH2" t="n">
-        <v>7.187169558164896e-06</v>
+        <v>0.01231569889932871</v>
       </c>
       <c r="CI2" t="n">
-        <v>8.709193934919313e-06</v>
+        <v>0.003142683999612927</v>
       </c>
       <c r="CJ2" t="n">
-        <v>4.504111984715564e-06</v>
+        <v>0.01911433413624763</v>
       </c>
       <c r="CK2" t="n">
-        <v>5.066362064098939e-06</v>
+        <v>0.01379632763564587</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.889903842311469e-06</v>
+        <v>0.00609036348760128</v>
       </c>
       <c r="CM2" t="n">
-        <v>4.029480805911589e-06</v>
+        <v>0.04030937701463699</v>
       </c>
       <c r="CN2" t="n">
-        <v>9.687678357295226e-07</v>
+        <v>0.004966966807842255</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.346961653325707e-08</v>
+        <v>0.02006447687745094</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.725843503663782e-05</v>
+        <v>0.05275380983948708</v>
       </c>
       <c r="CQ2" t="n">
-        <v>7.096211447787937e-06</v>
+        <v>0.01859147846698761</v>
       </c>
       <c r="CR2" t="n">
-        <v>7.551522003268474e-07</v>
+        <v>0.005763455759733915</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.78058632829925e-05</v>
+        <v>0.01758911088109016</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.436020779190585e-05</v>
+        <v>0.01479493547230959</v>
       </c>
       <c r="CU2" t="n">
-        <v>2.066413435386494e-05</v>
+        <v>0.02886996977031231</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.45327021527919e-05</v>
+        <v>0.008070286363363266</v>
       </c>
       <c r="CW2" t="n">
-        <v>5.448459887702484e-06</v>
+        <v>0.04513378441333771</v>
       </c>
       <c r="CX2" t="n">
-        <v>2.877914539567428e-06</v>
+        <v>0.02517220936715603</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.633995270822197e-05</v>
+        <v>0.05048607289791107</v>
       </c>
       <c r="CZ2" t="n">
-        <v>4.434848506207345e-06</v>
+        <v>0.0084487684071064</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.280333071917994e-05</v>
+        <v>0.003064879216253757</v>
       </c>
       <c r="DB2" t="n">
-        <v>2.333954853384057e-06</v>
+        <v>0.02257949486374855</v>
       </c>
       <c r="DC2" t="n">
-        <v>4.130546585656703e-06</v>
+        <v>0.01293762773275375</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.198322590629687e-06</v>
+        <v>0.01147790439426899</v>
       </c>
       <c r="DE2" t="n">
-        <v>2.964437499031192e-06</v>
+        <v>0.02019688673317432</v>
       </c>
       <c r="DF2" t="n">
-        <v>4.221648123348132e-05</v>
+        <v>0.1408209502696991</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.650777059898246e-05</v>
+        <v>0.05042154341936111</v>
       </c>
       <c r="DH2" t="n">
-        <v>1.441438962501707e-05</v>
+        <v>0.01300481706857681</v>
       </c>
       <c r="DI2" t="n">
-        <v>1.859149779193103e-05</v>
+        <v>0.005508970469236374</v>
       </c>
       <c r="DJ2" t="n">
-        <v>3.032801760127768e-05</v>
+        <v>0.01513417810201645</v>
       </c>
       <c r="DK2" t="n">
-        <v>3.796518285525963e-05</v>
+        <v>0.02029854618012905</v>
       </c>
       <c r="DL2" t="n">
-        <v>4.449846528586932e-06</v>
+        <v>0.002722525270655751</v>
       </c>
       <c r="DM2" t="n">
-        <v>1.838508978835307e-05</v>
+        <v>0.03947721421718597</v>
       </c>
       <c r="DN2" t="n">
-        <v>1.49933666762081e-05</v>
+        <v>0.009411361068487167</v>
       </c>
       <c r="DO2" t="n">
-        <v>6.603197562071728e-06</v>
+        <v>0.01743423752486706</v>
       </c>
       <c r="DP2" t="n">
-        <v>2.295591548318043e-05</v>
+        <v>0.04386882856488228</v>
       </c>
       <c r="DQ2" t="n">
-        <v>2.546479299780913e-05</v>
+        <v>0.01360104978084564</v>
       </c>
       <c r="DR2" t="n">
-        <v>3.776955054490827e-06</v>
+        <v>0.05646845698356628</v>
       </c>
       <c r="DS2" t="n">
-        <v>7.272838502103696e-06</v>
+        <v>0.09001277387142181</v>
       </c>
       <c r="DT2" t="n">
-        <v>4.087954948772676e-06</v>
+        <v>0.04887809231877327</v>
       </c>
       <c r="DU2" t="n">
-        <v>3.002888888659072e-06</v>
+        <v>0.06981667876243591</v>
       </c>
       <c r="DV2" t="n">
-        <v>7.720017492829356e-06</v>
+        <v>0.03749700635671616</v>
       </c>
       <c r="DW2" t="n">
-        <v>2.074707845167723e-05</v>
+        <v>0.03462266176939011</v>
       </c>
       <c r="DX2" t="n">
-        <v>9.219939784088638e-06</v>
+        <v>0.002845366252586246</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.793526831141207e-06</v>
+        <v>0.04360861331224442</v>
       </c>
       <c r="DZ2" t="n">
-        <v>1.212957067764364e-05</v>
+        <v>0.05448688566684723</v>
       </c>
       <c r="EA2" t="n">
-        <v>6.278477485466283e-06</v>
+        <v>0.1477057784795761</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.865035847004037e-05</v>
+        <v>0.1168074384331703</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.005557078315178e-05</v>
+        <v>0.008301407098770142</v>
       </c>
       <c r="ED2" t="n">
-        <v>1.989250267797615e-05</v>
+        <v>0.08189340680837631</v>
       </c>
       <c r="EE2" t="n">
-        <v>6.252369530557189e-06</v>
+        <v>0.01304634846746922</v>
       </c>
       <c r="EF2" t="n">
-        <v>7.993623967195163e-07</v>
+        <v>0.02157893776893616</v>
       </c>
       <c r="EG2" t="n">
-        <v>2.607014039313071e-06</v>
+        <v>0.03343143686652184</v>
       </c>
       <c r="EH2" t="n">
-        <v>8.115849823298049e-07</v>
+        <v>0.01800095289945602</v>
       </c>
       <c r="EI2" t="n">
-        <v>3.74638766516e-05</v>
+        <v>0.1394317150115967</v>
       </c>
       <c r="EJ2" t="n">
-        <v>6.782054697396234e-06</v>
+        <v>0.002378057688474655</v>
       </c>
       <c r="EK2" t="n">
-        <v>6.870845027151518e-06</v>
+        <v>0.02402741089463234</v>
       </c>
       <c r="EL2" t="n">
-        <v>7.919313702586805e-07</v>
+        <v>0.009199758991599083</v>
       </c>
       <c r="EM2" t="n">
-        <v>1.089604302251246e-05</v>
+        <v>0.009859059005975723</v>
       </c>
       <c r="EN2" t="n">
-        <v>4.321707820054144e-06</v>
+        <v>0.002917010802775621</v>
       </c>
       <c r="EO2" t="n">
-        <v>2.174809378630016e-05</v>
+        <v>0.004051649942994118</v>
       </c>
       <c r="EP2" t="n">
-        <v>7.927097840365604e-07</v>
+        <v>0.04357022047042847</v>
       </c>
       <c r="EQ2" t="n">
-        <v>1.698750929790549e-05</v>
+        <v>0.0190245658159256</v>
       </c>
       <c r="ER2" t="n">
-        <v>1.346261524304282e-05</v>
+        <v>0.01321094017475843</v>
       </c>
       <c r="ES2" t="n">
-        <v>1.537325374556531e-06</v>
+        <v>0.01055210828781128</v>
       </c>
       <c r="ET2" t="n">
-        <v>2.401125857431907e-05</v>
+        <v>0.01208071410655975</v>
       </c>
       <c r="EU2" t="n">
-        <v>4.296253791835625e-06</v>
+        <v>0.002246393822133541</v>
       </c>
       <c r="EV2" t="n">
-        <v>1.12869120130199e-05</v>
+        <v>0.003507426707074046</v>
       </c>
       <c r="EW2" t="n">
-        <v>7.411035767290741e-06</v>
+        <v>0.006205979734659195</v>
       </c>
       <c r="EX2" t="n">
-        <v>1.743296525091864e-05</v>
+        <v>0.001003840938210487</v>
       </c>
       <c r="EY2" t="n">
-        <v>4.817185526917456e-06</v>
+        <v>0.05842205882072449</v>
       </c>
       <c r="EZ2" t="n">
-        <v>3.506627763272263e-06</v>
+        <v>0.02353494055569172</v>
       </c>
       <c r="FA2" t="n">
-        <v>1.920977229019627e-05</v>
+        <v>0.04117598384618759</v>
       </c>
       <c r="FB2" t="n">
-        <v>8.298122338601388e-06</v>
+        <v>0.003818255849182606</v>
       </c>
       <c r="FC2" t="n">
-        <v>8.69910218170844e-06</v>
+        <v>0.01220933254808187</v>
       </c>
       <c r="FD2" t="n">
-        <v>6.732640258633182e-07</v>
+        <v>0.01757031120359898</v>
       </c>
       <c r="FE2" t="n">
-        <v>1.953035052792984e-06</v>
+        <v>0.004646892659366131</v>
       </c>
       <c r="FF2" t="n">
-        <v>7.325188107643044e-06</v>
+        <v>0.01228921767324209</v>
       </c>
       <c r="FG2" t="n">
-        <v>7.721186193521135e-06</v>
+        <v>0.02968498505651951</v>
       </c>
       <c r="FH2" t="n">
-        <v>2.389278597547673e-05</v>
+        <v>0.08206035196781158</v>
       </c>
       <c r="FI2" t="n">
-        <v>2.369913545408053e-06</v>
+        <v>0.05669296160340309</v>
       </c>
       <c r="FJ2" t="n">
-        <v>1.101532325264998e-05</v>
+        <v>0.02224896103143692</v>
       </c>
       <c r="FK2" t="n">
-        <v>1.169104052678449e-05</v>
+        <v>0.04415068775415421</v>
       </c>
       <c r="FL2" t="n">
-        <v>3.35230333803338e-06</v>
+        <v>0.0333191305398941</v>
       </c>
       <c r="FM2" t="n">
-        <v>1.06162269730703e-05</v>
+        <v>0.01752110011875629</v>
       </c>
       <c r="FN2" t="n">
-        <v>7.532275503763231e-06</v>
+        <v>0.1326403915882111</v>
       </c>
       <c r="FO2" t="n">
-        <v>3.640846671260078e-06</v>
+        <v>0.06435441970825195</v>
       </c>
       <c r="FP2" t="n">
-        <v>3.018453935510479e-05</v>
+        <v>0.07326196879148483</v>
       </c>
       <c r="FQ2" t="n">
-        <v>2.356036748096813e-05</v>
+        <v>0.02198098413646221</v>
       </c>
       <c r="FR2" t="n">
-        <v>8.679212442075368e-07</v>
+        <v>0.0686846449971199</v>
       </c>
       <c r="FS2" t="n">
-        <v>2.965669182231068e-06</v>
+        <v>0.1476925015449524</v>
       </c>
       <c r="FT2" t="n">
-        <v>7.716420441283844e-06</v>
+        <v>0.03456823155283928</v>
       </c>
       <c r="FU2" t="n">
-        <v>8.487926606903784e-06</v>
+        <v>0.07036636769771576</v>
       </c>
       <c r="FV2" t="n">
-        <v>5.36091611138545e-05</v>
+        <v>0.001809487119317055</v>
       </c>
       <c r="FW2" t="n">
-        <v>2.613078504509758e-05</v>
+        <v>0.02723518013954163</v>
       </c>
       <c r="FX2" t="n">
-        <v>7.268210538313724e-06</v>
+        <v>0.03723855689167976</v>
       </c>
       <c r="FY2" t="n">
-        <v>3.918037691619247e-05</v>
+        <v>0.003962086513638496</v>
       </c>
       <c r="FZ2" t="n">
-        <v>3.702712774611427e-06</v>
+        <v>0.02006128802895546</v>
       </c>
       <c r="GA2" t="n">
-        <v>3.205542816431262e-05</v>
+        <v>0.01287262514233589</v>
       </c>
       <c r="GB2" t="n">
-        <v>2.598051196400775e-06</v>
+        <v>0.02123705670237541</v>
       </c>
       <c r="GC2" t="n">
-        <v>2.76481696346309e-05</v>
+        <v>0.02421491593122482</v>
       </c>
       <c r="GD2" t="n">
-        <v>1.670164601819124e-05</v>
+        <v>0.04066874086856842</v>
       </c>
       <c r="GE2" t="n">
-        <v>2.622579086164478e-05</v>
+        <v>0.03719249740242958</v>
       </c>
       <c r="GF2" t="n">
-        <v>1.55230300151743e-05</v>
+        <v>0.01260396558791399</v>
       </c>
       <c r="GG2" t="n">
-        <v>1.650060403335374e-05</v>
+        <v>0.04258511587977409</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0</v>
+        <v>0.02492113970220089</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>0.005874051712453365</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>0.0002556489780545235</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>0.01333500165492296</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.005298501811921597</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>0.005145854316651821</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.0162992849946022</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>0.009580315090715885</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.005190610885620117</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>0.03079303167760372</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>0.007615178823471069</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.002558770822361112</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>0.007264862768352032</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>0.01183090265840292</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>0.003691870486363769</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.02634180895984173</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>0.006403781473636627</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>0.01730947569012642</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>0.002388807712122798</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>0.001922118943184614</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>0.002140033291652799</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.002309994772076607</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.003238531528040767</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.00686452304944396</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>0.002030926989391446</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>0.002897324739024043</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>0.000511993479449302</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>0.00125234154984355</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>0.003862980054691434</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>0.0002891207113862038</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>0.002428543753921986</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>0.009330287575721741</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>0.009024860337376595</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>7.030065171420574e-05</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>0.00346151296980679</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>0.0005113425431773067</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>0.003233867231756449</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>0.008323408663272858</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>0.004858489148318768</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>0.001319699455052614</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>0.005529214162379503</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>0.0008159666322171688</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>0.000737006077542901</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>0.0006346706068143249</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>0.001105641713365912</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>0.0181250236928463</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>0.003344759112223983</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>0.003617669455707073</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>0.004091707989573479</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>0.002262673806399107</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>0.002249930752441287</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>0.01024006586521864</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>0.009808127768337727</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>0.002842203248292208</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>0.004899363964796066</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>0.005609156098216772</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>0.001557238050736487</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>0.007645966485142708</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>0.001964283641427755</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>0.004248966462910175</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>0.0008360533975064754</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>0.008368426002562046</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>0.006406147964298725</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>0.004932848270982504</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>0.002559763845056295</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>0.0004416888987179846</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>0.003511219751089811</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>0.003621906507760286</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>0.00191468046978116</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>0.003314014757052064</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>0.004714908543974161</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>0.005285528022795916</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>0.008468315005302429</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>0.003713466227054596</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>0.00602275226265192</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>0.005550001282244921</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>0.0001434635778423399</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>4.942371742799878e-05</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>0.006193303037434816</v>
       </c>
       <c r="CB3" t="n">
-        <v>0</v>
+        <v>0.000502329901792109</v>
       </c>
       <c r="CC3" t="n">
-        <v>0</v>
+        <v>0.004057151731103659</v>
       </c>
       <c r="CD3" t="n">
-        <v>0</v>
+        <v>0.008010498248040676</v>
       </c>
       <c r="CE3" t="n">
-        <v>0</v>
+        <v>0.004534185398370028</v>
       </c>
       <c r="CF3" t="n">
-        <v>0</v>
+        <v>0.0001565402490086854</v>
       </c>
       <c r="CG3" t="n">
-        <v>0</v>
+        <v>0.003106437623500824</v>
       </c>
       <c r="CH3" t="n">
-        <v>0</v>
+        <v>0.002520727692171931</v>
       </c>
       <c r="CI3" t="n">
-        <v>0</v>
+        <v>0.001035626046359539</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0</v>
+        <v>0.003772563999518752</v>
       </c>
       <c r="CK3" t="n">
-        <v>0</v>
+        <v>3.07103618979454e-05</v>
       </c>
       <c r="CL3" t="n">
-        <v>0</v>
+        <v>0.0001667766773607582</v>
       </c>
       <c r="CM3" t="n">
-        <v>0</v>
+        <v>0.002985873259603977</v>
       </c>
       <c r="CN3" t="n">
-        <v>0</v>
+        <v>0.0171804279088974</v>
       </c>
       <c r="CO3" t="n">
-        <v>0</v>
+        <v>0.005982248112559319</v>
       </c>
       <c r="CP3" t="n">
-        <v>0</v>
+        <v>0.008850865066051483</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0</v>
+        <v>0.002501217648386955</v>
       </c>
       <c r="CR3" t="n">
-        <v>0</v>
+        <v>0.01507183071225882</v>
       </c>
       <c r="CS3" t="n">
-        <v>0</v>
+        <v>0.01096892170608044</v>
       </c>
       <c r="CT3" t="n">
-        <v>0</v>
+        <v>0.00551024591550231</v>
       </c>
       <c r="CU3" t="n">
-        <v>0</v>
+        <v>0.005272840149700642</v>
       </c>
       <c r="CV3" t="n">
-        <v>0</v>
+        <v>0.007479837629944086</v>
       </c>
       <c r="CW3" t="n">
-        <v>0</v>
+        <v>0.003985339775681496</v>
       </c>
       <c r="CX3" t="n">
-        <v>0</v>
+        <v>0.0005808243295177817</v>
       </c>
       <c r="CY3" t="n">
-        <v>0</v>
+        <v>0.00259419297799468</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0</v>
+        <v>0.004459374118596315</v>
       </c>
       <c r="DA3" t="n">
-        <v>0</v>
+        <v>0.002008479088544846</v>
       </c>
       <c r="DB3" t="n">
-        <v>0</v>
+        <v>0.004542597569525242</v>
       </c>
       <c r="DC3" t="n">
-        <v>0</v>
+        <v>0.001191947842016816</v>
       </c>
       <c r="DD3" t="n">
-        <v>0</v>
+        <v>0.0003685923584271222</v>
       </c>
       <c r="DE3" t="n">
-        <v>0</v>
+        <v>0.005269519053399563</v>
       </c>
       <c r="DF3" t="n">
-        <v>0</v>
+        <v>0.008162619546055794</v>
       </c>
       <c r="DG3" t="n">
-        <v>0</v>
+        <v>0.0005500458646565676</v>
       </c>
       <c r="DH3" t="n">
-        <v>0</v>
+        <v>0.003570258151739836</v>
       </c>
       <c r="DI3" t="n">
-        <v>0</v>
+        <v>0.01388313807547092</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0</v>
+        <v>0.002551981713622808</v>
       </c>
       <c r="DK3" t="n">
-        <v>0</v>
+        <v>0.004098694305866957</v>
       </c>
       <c r="DL3" t="n">
-        <v>0</v>
+        <v>0.004410937894135714</v>
       </c>
       <c r="DM3" t="n">
-        <v>0</v>
+        <v>0.003625881858170033</v>
       </c>
       <c r="DN3" t="n">
-        <v>0</v>
+        <v>0.00177074468228966</v>
       </c>
       <c r="DO3" t="n">
-        <v>0</v>
+        <v>0.00365559128113091</v>
       </c>
       <c r="DP3" t="n">
-        <v>0</v>
+        <v>0.0001567471772432327</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0</v>
+        <v>0.001388271106407046</v>
       </c>
       <c r="DR3" t="n">
-        <v>0</v>
+        <v>0.001784457825124264</v>
       </c>
       <c r="DS3" t="n">
-        <v>0</v>
+        <v>0.00549100898206234</v>
       </c>
       <c r="DT3" t="n">
-        <v>0</v>
+        <v>0.002586463699117303</v>
       </c>
       <c r="DU3" t="n">
-        <v>0</v>
+        <v>0.003749729134142399</v>
       </c>
       <c r="DV3" t="n">
-        <v>0</v>
+        <v>0.0034826819319278</v>
       </c>
       <c r="DW3" t="n">
-        <v>0</v>
+        <v>0.001532334950752556</v>
       </c>
       <c r="DX3" t="n">
-        <v>0</v>
+        <v>0.006957496516406536</v>
       </c>
       <c r="DY3" t="n">
-        <v>0</v>
+        <v>0.0008446271531283855</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0</v>
+        <v>0.0009510715608485043</v>
       </c>
       <c r="EA3" t="n">
-        <v>0</v>
+        <v>0.005694426596164703</v>
       </c>
       <c r="EB3" t="n">
-        <v>0</v>
+        <v>0.01053172629326582</v>
       </c>
       <c r="EC3" t="n">
-        <v>0</v>
+        <v>0.01366953551769257</v>
       </c>
       <c r="ED3" t="n">
-        <v>0</v>
+        <v>0.00862516462802887</v>
       </c>
       <c r="EE3" t="n">
-        <v>0</v>
+        <v>0.007061542943120003</v>
       </c>
       <c r="EF3" t="n">
-        <v>0</v>
+        <v>0.006203517783433199</v>
       </c>
       <c r="EG3" t="n">
-        <v>0</v>
+        <v>0.002886326517909765</v>
       </c>
       <c r="EH3" t="n">
-        <v>0</v>
+        <v>0.0001753375399857759</v>
       </c>
       <c r="EI3" t="n">
-        <v>0</v>
+        <v>0.011800198815763</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0</v>
+        <v>0.0002647272776812315</v>
       </c>
       <c r="EK3" t="n">
-        <v>0</v>
+        <v>0.0007627996965311468</v>
       </c>
       <c r="EL3" t="n">
-        <v>0</v>
+        <v>0.003161799861118197</v>
       </c>
       <c r="EM3" t="n">
-        <v>0</v>
+        <v>0.003096894826740026</v>
       </c>
       <c r="EN3" t="n">
-        <v>0</v>
+        <v>0.00249817781150341</v>
       </c>
       <c r="EO3" t="n">
-        <v>0</v>
+        <v>0.00885437149554491</v>
       </c>
       <c r="EP3" t="n">
-        <v>0</v>
+        <v>0.002343523316085339</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0</v>
+        <v>0.004241213668137789</v>
       </c>
       <c r="ER3" t="n">
-        <v>0</v>
+        <v>0.002412439556792378</v>
       </c>
       <c r="ES3" t="n">
-        <v>0</v>
+        <v>0.009463573805987835</v>
       </c>
       <c r="ET3" t="n">
-        <v>0</v>
+        <v>0.002651255112141371</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>0.00326872686855495</v>
       </c>
       <c r="EV3" t="n">
-        <v>0</v>
+        <v>0.004639312624931335</v>
       </c>
       <c r="EW3" t="n">
-        <v>0</v>
+        <v>0.007032485678792</v>
       </c>
       <c r="EX3" t="n">
-        <v>0</v>
+        <v>0.009568708948791027</v>
       </c>
       <c r="EY3" t="n">
-        <v>0</v>
+        <v>0.006183657329529524</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0</v>
+        <v>0.0008372542215511203</v>
       </c>
       <c r="FA3" t="n">
-        <v>0</v>
+        <v>0.003296209499239922</v>
       </c>
       <c r="FB3" t="n">
-        <v>0</v>
+        <v>0.003174851182848215</v>
       </c>
       <c r="FC3" t="n">
-        <v>0</v>
+        <v>0.0009273395990021527</v>
       </c>
       <c r="FD3" t="n">
-        <v>0</v>
+        <v>0.005554608069360256</v>
       </c>
       <c r="FE3" t="n">
-        <v>0</v>
+        <v>0.001842159777879715</v>
       </c>
       <c r="FF3" t="n">
-        <v>0</v>
+        <v>0.001577266491949558</v>
       </c>
       <c r="FG3" t="n">
-        <v>0</v>
+        <v>0.006877649575471878</v>
       </c>
       <c r="FH3" t="n">
-        <v>0</v>
+        <v>0.003455917118117213</v>
       </c>
       <c r="FI3" t="n">
-        <v>0</v>
+        <v>0.004483694210648537</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0</v>
+        <v>0.0006426111795008183</v>
       </c>
       <c r="FK3" t="n">
-        <v>0</v>
+        <v>0.002255448838695884</v>
       </c>
       <c r="FL3" t="n">
-        <v>0</v>
+        <v>0.002955419709905982</v>
       </c>
       <c r="FM3" t="n">
-        <v>0</v>
+        <v>0.0005201121093705297</v>
       </c>
       <c r="FN3" t="n">
-        <v>0</v>
+        <v>0.0001879933115560561</v>
       </c>
       <c r="FO3" t="n">
-        <v>0</v>
+        <v>0.001358803943730891</v>
       </c>
       <c r="FP3" t="n">
-        <v>0</v>
+        <v>0.01258015725761652</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0</v>
+        <v>0.01238122768700123</v>
       </c>
       <c r="FR3" t="n">
-        <v>0</v>
+        <v>0.01348523329943419</v>
       </c>
       <c r="FS3" t="n">
-        <v>0</v>
+        <v>0.007283957209438086</v>
       </c>
       <c r="FT3" t="n">
-        <v>0</v>
+        <v>0.01266664452850819</v>
       </c>
       <c r="FU3" t="n">
-        <v>0</v>
+        <v>0.008277036249637604</v>
       </c>
       <c r="FV3" t="n">
-        <v>0</v>
+        <v>0.007827679626643658</v>
       </c>
       <c r="FW3" t="n">
-        <v>0</v>
+        <v>0.002192466054111719</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>0.006719547789543867</v>
       </c>
       <c r="FY3" t="n">
-        <v>0</v>
+        <v>0.004876556806266308</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0</v>
+        <v>0.001017862930893898</v>
       </c>
       <c r="GA3" t="n">
-        <v>0</v>
+        <v>0.004116191063076258</v>
       </c>
       <c r="GB3" t="n">
-        <v>0</v>
+        <v>0.002382952254265547</v>
       </c>
       <c r="GC3" t="n">
-        <v>0</v>
+        <v>0.0002662329352460802</v>
       </c>
       <c r="GD3" t="n">
-        <v>0</v>
+        <v>0.01070589572191238</v>
       </c>
       <c r="GE3" t="n">
-        <v>0</v>
+        <v>0.01012512110173702</v>
       </c>
       <c r="GF3" t="n">
-        <v>0</v>
+        <v>0.004554364830255508</v>
       </c>
       <c r="GG3" t="n">
+        <v>0.005063304211944342</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.1996440291404724</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.8185970783233643</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.09479822218418121</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1756348311901093</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.1772956103086472</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8138975501060486</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.1307673454284668</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.1552716195583344</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.03331624716520309</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.05665818601846695</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.8451331257820129</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.006544440984725952</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.1115931272506714</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.1969549059867859</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.6693657636642456</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.1158555597066879</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.1494599282741547</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.01500794291496277</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.1253880709409714</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.2237526327371597</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.3129101693630219</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.1780339181423187</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.1618795841932297</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.1110475137829781</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.4090975224971771</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.2146796137094498</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.09733268618583679</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.2492498457431793</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.1587561666965485</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.05424502491950989</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.4974962472915649</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.04106885939836502</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.2004928141832352</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.1959169507026672</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.263545423746109</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.2215875536203384</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.04785331711173058</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.03605330735445023</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.001541383564472198</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.09694883972406387</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.1592272967100143</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0.1702902764081955</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.2751232385635376</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.1146075204014778</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0.05961372330784798</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0.05274616926908493</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.4235699474811554</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.1394388973712921</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.1075722202658653</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0.4509218037128448</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0.4472329914569855</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0.1945671290159225</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0.08405475318431854</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0.1309990733861923</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0.1407968252897263</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0.5937376022338867</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0.07133749127388</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0.3607815206050873</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0.4220349192619324</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>0.2719989418983459</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>0.08731858432292938</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.2446861863136292</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.1504059731960297</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0.0777568519115448</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0.08255529403686523</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>0.0496213510632515</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>0.02097015827894211</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>0.08497397601604462</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>0.1562537550926208</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>0.0708046481013298</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>0.09074043482542038</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>0.07013304531574249</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>0.05147172510623932</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>0.1442889422178268</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>0.2379716634750366</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>0.1194369941949844</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>0.1525925993919373</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>0.3750940561294556</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>0.4534981548786163</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>0.06456635147333145</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>0.006425042171031237</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>0.05212147161364555</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>0.2221844345331192</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>0.05273189768195152</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>0.07996206730604172</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>0.04449086636304855</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>0.1865569055080414</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>0.01128828246146441</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>0.01376334112137556</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>0.01878855936229229</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>0.2728427648544312</v>
+      </c>
+      <c r="CN4" t="n">
+        <v>0.5171961188316345</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>0.3292666375637054</v>
+      </c>
+      <c r="CP4" t="n">
+        <v>0.2255361825227737</v>
+      </c>
+      <c r="CQ4" t="n">
+        <v>0.07470910251140594</v>
+      </c>
+      <c r="CR4" t="n">
+        <v>0.2316506206989288</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>0.0108543960377574</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>0.1510039716959</v>
+      </c>
+      <c r="CU4" t="n">
+        <v>0.1890023946762085</v>
+      </c>
+      <c r="CV4" t="n">
+        <v>0.03959941864013672</v>
+      </c>
+      <c r="CW4" t="n">
+        <v>0.20718714594841</v>
+      </c>
+      <c r="CX4" t="n">
+        <v>0.003065629862248898</v>
+      </c>
+      <c r="CY4" t="n">
+        <v>0.04103329032659531</v>
+      </c>
+      <c r="CZ4" t="n">
+        <v>0.03238403052091599</v>
+      </c>
+      <c r="DA4" t="n">
+        <v>0.1586460471153259</v>
+      </c>
+      <c r="DB4" t="n">
+        <v>0.02107599005103111</v>
+      </c>
+      <c r="DC4" t="n">
+        <v>0.02865760028362274</v>
+      </c>
+      <c r="DD4" t="n">
+        <v>0.01008343696594238</v>
+      </c>
+      <c r="DE4" t="n">
+        <v>0.3547394275665283</v>
+      </c>
+      <c r="DF4" t="n">
+        <v>0.1664819866418839</v>
+      </c>
+      <c r="DG4" t="n">
+        <v>0.2957070767879486</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>0.1036640182137489</v>
+      </c>
+      <c r="DI4" t="n">
+        <v>0.1384228616952896</v>
+      </c>
+      <c r="DJ4" t="n">
+        <v>0.549643337726593</v>
+      </c>
+      <c r="DK4" t="n">
+        <v>0.1609552502632141</v>
+      </c>
+      <c r="DL4" t="n">
+        <v>0.1169019043445587</v>
+      </c>
+      <c r="DM4" t="n">
+        <v>0.1883677542209625</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>0.03587297350168228</v>
+      </c>
+      <c r="DO4" t="n">
+        <v>0.1786002516746521</v>
+      </c>
+      <c r="DP4" t="n">
+        <v>0.1190716326236725</v>
+      </c>
+      <c r="DQ4" t="n">
+        <v>0.2868355810642242</v>
+      </c>
+      <c r="DR4" t="n">
+        <v>0.06015627086162567</v>
+      </c>
+      <c r="DS4" t="n">
+        <v>0.07379718869924545</v>
+      </c>
+      <c r="DT4" t="n">
+        <v>0.04751647263765335</v>
+      </c>
+      <c r="DU4" t="n">
+        <v>0.08084291964769363</v>
+      </c>
+      <c r="DV4" t="n">
+        <v>0.05688132345676422</v>
+      </c>
+      <c r="DW4" t="n">
+        <v>0.134099006652832</v>
+      </c>
+      <c r="DX4" t="n">
+        <v>0.1529425233602524</v>
+      </c>
+      <c r="DY4" t="n">
+        <v>0.05104942247271538</v>
+      </c>
+      <c r="DZ4" t="n">
+        <v>0.01611297950148582</v>
+      </c>
+      <c r="EA4" t="n">
+        <v>0.1616726815700531</v>
+      </c>
+      <c r="EB4" t="n">
+        <v>0.3012206554412842</v>
+      </c>
+      <c r="EC4" t="n">
+        <v>0.03315120190382004</v>
+      </c>
+      <c r="ED4" t="n">
+        <v>0.2559876441955566</v>
+      </c>
+      <c r="EE4" t="n">
+        <v>0.2675755620002747</v>
+      </c>
+      <c r="EF4" t="n">
+        <v>0.07689057290554047</v>
+      </c>
+      <c r="EG4" t="n">
+        <v>0.08744347095489502</v>
+      </c>
+      <c r="EH4" t="n">
+        <v>0.1126923188567162</v>
+      </c>
+      <c r="EI4" t="n">
+        <v>0.1701201945543289</v>
+      </c>
+      <c r="EJ4" t="n">
+        <v>0.04028697311878204</v>
+      </c>
+      <c r="EK4" t="n">
+        <v>0.22177454829216</v>
+      </c>
+      <c r="EL4" t="n">
+        <v>0.09126404672861099</v>
+      </c>
+      <c r="EM4" t="n">
+        <v>0.08474180102348328</v>
+      </c>
+      <c r="EN4" t="n">
+        <v>0.02203127928078175</v>
+      </c>
+      <c r="EO4" t="n">
+        <v>0.07594318687915802</v>
+      </c>
+      <c r="EP4" t="n">
+        <v>0.132783830165863</v>
+      </c>
+      <c r="EQ4" t="n">
+        <v>0.2167079746723175</v>
+      </c>
+      <c r="ER4" t="n">
+        <v>0.1768475323915482</v>
+      </c>
+      <c r="ES4" t="n">
+        <v>0.2786274254322052</v>
+      </c>
+      <c r="ET4" t="n">
+        <v>0.2565068900585175</v>
+      </c>
+      <c r="EU4" t="n">
+        <v>0.02878407016396523</v>
+      </c>
+      <c r="EV4" t="n">
+        <v>0.08820487558841705</v>
+      </c>
+      <c r="EW4" t="n">
+        <v>0.02388534508645535</v>
+      </c>
+      <c r="EX4" t="n">
+        <v>0.04853880032896996</v>
+      </c>
+      <c r="EY4" t="n">
+        <v>0.1862277686595917</v>
+      </c>
+      <c r="EZ4" t="n">
+        <v>0.00411927467212081</v>
+      </c>
+      <c r="FA4" t="n">
+        <v>0.02603213489055634</v>
+      </c>
+      <c r="FB4" t="n">
+        <v>0.09720851480960846</v>
+      </c>
+      <c r="FC4" t="n">
+        <v>0.1642074584960938</v>
+      </c>
+      <c r="FD4" t="n">
+        <v>7.832050323486328e-05</v>
+      </c>
+      <c r="FE4" t="n">
+        <v>0.0116312624886632</v>
+      </c>
+      <c r="FF4" t="n">
+        <v>0.02201509103178978</v>
+      </c>
+      <c r="FG4" t="n">
+        <v>0.2080128788948059</v>
+      </c>
+      <c r="FH4" t="n">
+        <v>0.03103601187467575</v>
+      </c>
+      <c r="FI4" t="n">
+        <v>0.1757827401161194</v>
+      </c>
+      <c r="FJ4" t="n">
+        <v>0.03869352862238884</v>
+      </c>
+      <c r="FK4" t="n">
+        <v>0.1185854971408844</v>
+      </c>
+      <c r="FL4" t="n">
+        <v>0.2728868722915649</v>
+      </c>
+      <c r="FM4" t="n">
+        <v>0.1422426700592041</v>
+      </c>
+      <c r="FN4" t="n">
+        <v>0.1550823003053665</v>
+      </c>
+      <c r="FO4" t="n">
+        <v>0.3290354311466217</v>
+      </c>
+      <c r="FP4" t="n">
+        <v>0.3719867765903473</v>
+      </c>
+      <c r="FQ4" t="n">
+        <v>0.2575177848339081</v>
+      </c>
+      <c r="FR4" t="n">
+        <v>0.1336212456226349</v>
+      </c>
+      <c r="FS4" t="n">
+        <v>0.06675948202610016</v>
+      </c>
+      <c r="FT4" t="n">
+        <v>0.01969285681843758</v>
+      </c>
+      <c r="FU4" t="n">
+        <v>0.05188720300793648</v>
+      </c>
+      <c r="FV4" t="n">
+        <v>0.07199816405773163</v>
+      </c>
+      <c r="FW4" t="n">
+        <v>0.03691750764846802</v>
+      </c>
+      <c r="FX4" t="n">
+        <v>0.095929354429245</v>
+      </c>
+      <c r="FY4" t="n">
+        <v>0.2563976645469666</v>
+      </c>
+      <c r="FZ4" t="n">
+        <v>0.05345506221055984</v>
+      </c>
+      <c r="GA4" t="n">
+        <v>0.05393135920166969</v>
+      </c>
+      <c r="GB4" t="n">
+        <v>0.06274798512458801</v>
+      </c>
+      <c r="GC4" t="n">
+        <v>0.3557769060134888</v>
+      </c>
+      <c r="GD4" t="n">
+        <v>0.2383796721696854</v>
+      </c>
+      <c r="GE4" t="n">
+        <v>0.1323489546775818</v>
+      </c>
+      <c r="GF4" t="n">
+        <v>0.1780464947223663</v>
+      </c>
+      <c r="GG4" t="n">
+        <v>0.295472115278244</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>0.04274788498878479</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.1985641866922379</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.06279755383729935</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6.902217864990234e-05</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.01494553126394749</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2177845388650894</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.03318588435649872</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.07796457409858704</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.03503086045384407</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.00773952528834343</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.2429612576961517</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.0844450369477272</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.05778256803750992</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.09703915566205978</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.230295717716217</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.01859778724610806</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.019756143912673</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.03602819517254829</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.002556517487391829</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.03482724726200104</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.03787796199321747</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.07818181067705154</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.07380577921867371</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.04068157449364662</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.00306851789355278</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.02714821696281433</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.02748582325875759</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.001856087706983089</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.03480810672044754</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.02850962616503239</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.06882181763648987</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.09218945354223251</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.04258444532752037</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.006876847706735134</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.1357539147138596</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.005232581868767738</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.001786720938980579</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.05748472362756729</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.0322720967233181</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0.04654843732714653</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.01949595846235752</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0.02003973349928856</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.01667273603379726</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0.04702454805374146</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0.04895887523889542</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0.01570279896259308</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.2644031941890717</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0.0545644611120224</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.02048908174037933</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0.08080814033746719</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0.1369764059782028</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0.03350933268666267</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0.005168456118553877</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0.02890630066394806</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0.009282858110964298</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0.0425005778670311</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0.04193765670061111</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0.006121167913079262</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>3.120210021734238e-05</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>0.002185911405831575</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0.01826617866754532</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0.0421023890376091</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0.007500936277210712</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0.01733939908444881</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0.04133942723274231</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>0.01085928734391928</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>0.03315318003296852</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0.01889372617006302</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0.03074240311980247</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>0.09830316156148911</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>0.001242600148543715</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>0.03819838166236877</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>0.01507354620844126</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>0.154304563999176</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>0.03487997502088547</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>0.08395707607269287</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>0.04511786252260208</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>0.09395170956850052</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>0.01597481966018677</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>0.000533323734998703</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>0.03303797170519829</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>0.004697342868894339</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>0.06967534869909286</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>0.009733736515045166</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0.02094398066401482</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>0.0006093988195061684</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>0.05122599005699158</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0.02543773874640465</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0.0153410704806447</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>0.01713013276457787</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>0.05174789577722549</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>0.09854447096586227</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>0.06023463606834412</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>0.06963817775249481</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>0.04346224665641785</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>0.00168485171161592</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>0.04380989819765091</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>0.00728957075625658</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>0.0002828959841281176</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>0.008252508938312531</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>0.05956113710999489</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>0.01428256276994944</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>0.01201269403100014</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>0.007153024431318045</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>0.05710932612419128</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>0.01612225361168385</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>0.01303092297166586</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>0.01473819091916084</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>0.03463071584701538</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>0.02193403616547585</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>0.03982523083686829</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>0.00700078159570694</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>0.03687978535890579</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>0.0664091631770134</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>0.01198296248912811</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>0.05542153120040894</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>0.006224688142538071</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>0.01631001010537148</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>0.03310753405094147</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>0.009839039295911789</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>0.02825773693621159</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>0.01654639840126038</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>0.0175052098929882</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>0.006139248609542847</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>0.03525322303175926</v>
+      </c>
+      <c r="DV6" t="n">
+        <v>0.02424080669879913</v>
+      </c>
+      <c r="DW6" t="n">
+        <v>0.02357620932161808</v>
+      </c>
+      <c r="DX6" t="n">
+        <v>0.01079647149890661</v>
+      </c>
+      <c r="DY6" t="n">
+        <v>0.03916829824447632</v>
+      </c>
+      <c r="DZ6" t="n">
+        <v>0.03406269103288651</v>
+      </c>
+      <c r="EA6" t="n">
+        <v>0.004302022978663445</v>
+      </c>
+      <c r="EB6" t="n">
+        <v>0.06162579357624054</v>
+      </c>
+      <c r="EC6" t="n">
+        <v>0.002498541492968798</v>
+      </c>
+      <c r="ED6" t="n">
+        <v>0.0005827220156788826</v>
+      </c>
+      <c r="EE6" t="n">
+        <v>0.04541299492120743</v>
+      </c>
+      <c r="EF6" t="n">
+        <v>0.0009377682581543922</v>
+      </c>
+      <c r="EG6" t="n">
+        <v>0.007365813013166189</v>
+      </c>
+      <c r="EH6" t="n">
+        <v>0.01504365541040897</v>
+      </c>
+      <c r="EI6" t="n">
+        <v>0.06447025388479233</v>
+      </c>
+      <c r="EJ6" t="n">
+        <v>0.02592779695987701</v>
+      </c>
+      <c r="EK6" t="n">
+        <v>0.02802845276892185</v>
+      </c>
+      <c r="EL6" t="n">
+        <v>0.003685468807816505</v>
+      </c>
+      <c r="EM6" t="n">
+        <v>0.002986038802191615</v>
+      </c>
+      <c r="EN6" t="n">
+        <v>0.01474350597709417</v>
+      </c>
+      <c r="EO6" t="n">
+        <v>0.00337462592869997</v>
+      </c>
+      <c r="EP6" t="n">
+        <v>0.0372445210814476</v>
+      </c>
+      <c r="EQ6" t="n">
+        <v>0.01855854876339436</v>
+      </c>
+      <c r="ER6" t="n">
+        <v>0.006150403060019016</v>
+      </c>
+      <c r="ES6" t="n">
+        <v>0.03360573947429657</v>
+      </c>
+      <c r="ET6" t="n">
+        <v>0.01956924796104431</v>
+      </c>
+      <c r="EU6" t="n">
+        <v>0.01532371062785387</v>
+      </c>
+      <c r="EV6" t="n">
+        <v>0.01103513967245817</v>
+      </c>
+      <c r="EW6" t="n">
+        <v>0.00261604180559516</v>
+      </c>
+      <c r="EX6" t="n">
+        <v>0.0004288270138204098</v>
+      </c>
+      <c r="EY6" t="n">
+        <v>0.07288022339344025</v>
+      </c>
+      <c r="EZ6" t="n">
+        <v>0.01185255497694016</v>
+      </c>
+      <c r="FA6" t="n">
+        <v>0.0123577993363142</v>
+      </c>
+      <c r="FB6" t="n">
+        <v>0.004478046204894781</v>
+      </c>
+      <c r="FC6" t="n">
+        <v>0.05280914157629013</v>
+      </c>
+      <c r="FD6" t="n">
+        <v>0.02853348851203918</v>
+      </c>
+      <c r="FE6" t="n">
+        <v>0.01463695336133242</v>
+      </c>
+      <c r="FF6" t="n">
+        <v>0.0008782613440416753</v>
+      </c>
+      <c r="FG6" t="n">
+        <v>0.001034172018989921</v>
+      </c>
+      <c r="FH6" t="n">
+        <v>0.06643643975257874</v>
+      </c>
+      <c r="FI6" t="n">
+        <v>0.03512898460030556</v>
+      </c>
+      <c r="FJ6" t="n">
+        <v>0.01400948874652386</v>
+      </c>
+      <c r="FK6" t="n">
+        <v>0.01588787510991096</v>
+      </c>
+      <c r="FL6" t="n">
+        <v>0.06943174451589584</v>
+      </c>
+      <c r="FM6" t="n">
+        <v>0.03384136036038399</v>
+      </c>
+      <c r="FN6" t="n">
+        <v>0.09331504255533218</v>
+      </c>
+      <c r="FO6" t="n">
+        <v>0.0633772537112236</v>
+      </c>
+      <c r="FP6" t="n">
+        <v>0.02037614211440086</v>
+      </c>
+      <c r="FQ6" t="n">
+        <v>0.07934047281742096</v>
+      </c>
+      <c r="FR6" t="n">
+        <v>0.04853487759828568</v>
+      </c>
+      <c r="FS6" t="n">
+        <v>0.05357223004102707</v>
+      </c>
+      <c r="FT6" t="n">
+        <v>0.03708913922309875</v>
+      </c>
+      <c r="FU6" t="n">
+        <v>0.06764524430036545</v>
+      </c>
+      <c r="FV6" t="n">
+        <v>0.0170227587223053</v>
+      </c>
+      <c r="FW6" t="n">
+        <v>0.08751505613327026</v>
+      </c>
+      <c r="FX6" t="n">
+        <v>0.03783002868294716</v>
+      </c>
+      <c r="FY6" t="n">
+        <v>0.02346868067979813</v>
+      </c>
+      <c r="FZ6" t="n">
+        <v>0.005067612044513226</v>
+      </c>
+      <c r="GA6" t="n">
+        <v>0.04710423201322556</v>
+      </c>
+      <c r="GB6" t="n">
+        <v>0.009069499559700489</v>
+      </c>
+      <c r="GC6" t="n">
+        <v>0.07691675424575806</v>
+      </c>
+      <c r="GD6" t="n">
+        <v>0.06030585989356041</v>
+      </c>
+      <c r="GE6" t="n">
+        <v>0.01779799163341522</v>
+      </c>
+      <c r="GF6" t="n">
+        <v>0.01419948041439056</v>
+      </c>
+      <c r="GG6" t="n">
+        <v>0.03733616322278976</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0.3684241771697998</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.5056469440460205</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.0480915829539299</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.04646874964237213</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.01630955561995506</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.4615721702575684</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.09244799613952637</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.1922777593135834</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.1361053436994553</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.3512128889560699</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.6405065059661865</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.07928036898374557</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.07385784387588501</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.22015580534935</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.4819891154766083</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.1215360835194588</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.04952829331159592</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.242059126496315</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.02370190806686878</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.07832897454500198</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.09711681306362152</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.1903809607028961</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.1192519813776016</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.1086773574352264</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.02133133634924889</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.2017495036125183</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.0820234939455986</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.1167286336421967</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.1194359585642815</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.05654007196426392</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.1778172701597214</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.3064426481723785</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.09612054377794266</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.0266825444996357</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.1894682198762894</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.04831349104642868</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.1180256903171539</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.1566746830940247</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.1146007180213928</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0.1239092946052551</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.09889949858188629</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0.033907201141119</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0.07471964508295059</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0.1522051692008972</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0.1429110169410706</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0.2499417364597321</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0.4601344168186188</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0.08230705559253693</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0.04220305755734444</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0.1679091900587082</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0.2713358998298645</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0.018601194024086</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0.001680184621363878</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0.1297606974840164</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0.04889420419931412</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0.0474449098110199</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0.08007586747407913</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0.0572580024600029</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0.001101935282349586</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0.1191649585962296</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0.03216880932450294</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0.05762013792991638</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0.06542056053876877</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0.01957434415817261</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0.01007078215479851</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>0.004560644272714853</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0.06463281810283661</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0.01010215748101473</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0.06139001250267029</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0.2293202728033066</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>0.04830429702997208</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0.09465257078409195</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>0.0789305567741394</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>0.3080325126647949</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0.07646404206752777</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>0.1364651620388031</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>0.0745716467499733</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>0.2493391335010529</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0.0001061074435710907</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>0.06445391476154327</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0.09966601431369781</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>0.05087818205356598</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>0.1732605844736099</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>0.02098995260894299</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0.02762548625469208</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>0.02348246611654758</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>0.1450214236974716</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0.1052058190107346</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0.04812078177928925</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>0.04266299307346344</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>0.03858351707458496</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>0.2725740373134613</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>0.06962116807699203</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>0.1857435256242752</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>0.08802550286054611</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>0.192963182926178</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>0.03095955774188042</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>0.02614050917327404</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>0.006864335387945175</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>0.03337936848402023</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>0.1577736735343933</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>0.02744672447443008</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>0.0134333111345768</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>0.007524414919316769</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>0.1422683298587799</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>0.07629023492336273</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>0.07790248095989227</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>0.04171805828809738</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>0.04770998284220695</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>0.04431309551000595</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>0.0881342887878418</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>0.05248367786407471</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>0.2872670888900757</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>0.05675574764609337</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>0.01012317463755608</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>0.06718067079782486</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>0.1262279599905014</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>0.04640001058578491</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>0.1048993617296219</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>0.06772793829441071</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>1.356005668640137e-05</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>0.05073916167020798</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>0.1827629655599594</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>0.05775142088532448</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>0.2226361483335495</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>0.04307795688509941</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>0.08189526200294495</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>0.02277187816798687</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>0.04273786023259163</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>0.1134069338440895</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>0.2194472253322601</v>
+      </c>
+      <c r="EB7" t="n">
+        <v>0.2290872186422348</v>
+      </c>
+      <c r="EC7" t="n">
+        <v>0.03206761926412582</v>
+      </c>
+      <c r="ED7" t="n">
+        <v>0.03084685280919075</v>
+      </c>
+      <c r="EE7" t="n">
+        <v>0.07885808497667313</v>
+      </c>
+      <c r="EF7" t="n">
+        <v>0.06019686162471771</v>
+      </c>
+      <c r="EG7" t="n">
+        <v>0.01358290947973728</v>
+      </c>
+      <c r="EH7" t="n">
+        <v>0.09004626423120499</v>
+      </c>
+      <c r="EI7" t="n">
+        <v>0.2056706249713898</v>
+      </c>
+      <c r="EJ7" t="n">
+        <v>0.03724781051278114</v>
+      </c>
+      <c r="EK7" t="n">
+        <v>0.07162865996360779</v>
+      </c>
+      <c r="EL7" t="n">
+        <v>0.06213466078042984</v>
+      </c>
+      <c r="EM7" t="n">
+        <v>0.03722188994288445</v>
+      </c>
+      <c r="EN7" t="n">
+        <v>0.03986339643597603</v>
+      </c>
+      <c r="EO7" t="n">
+        <v>0.03720734268426895</v>
+      </c>
+      <c r="EP7" t="n">
+        <v>0.05736091360449791</v>
+      </c>
+      <c r="EQ7" t="n">
+        <v>0.02915674820542336</v>
+      </c>
+      <c r="ER7" t="n">
+        <v>0.02032032981514931</v>
+      </c>
+      <c r="ES7" t="n">
+        <v>0.01891227066516876</v>
+      </c>
+      <c r="ET7" t="n">
+        <v>0.1110989823937416</v>
+      </c>
+      <c r="EU7" t="n">
+        <v>0.03296542167663574</v>
+      </c>
+      <c r="EV7" t="n">
+        <v>0.05384489893913269</v>
+      </c>
+      <c r="EW7" t="n">
+        <v>0.1313600689172745</v>
+      </c>
+      <c r="EX7" t="n">
+        <v>0.04972962662577629</v>
+      </c>
+      <c r="EY7" t="n">
+        <v>0.1935281306505203</v>
+      </c>
+      <c r="EZ7" t="n">
+        <v>0.01313954405486584</v>
+      </c>
+      <c r="FA7" t="n">
+        <v>0.01396398991346359</v>
+      </c>
+      <c r="FB7" t="n">
+        <v>0.0314975306391716</v>
+      </c>
+      <c r="FC7" t="n">
+        <v>0.1361992955207825</v>
+      </c>
+      <c r="FD7" t="n">
+        <v>0.0995117723941803</v>
+      </c>
+      <c r="FE7" t="n">
+        <v>0.0838705450296402</v>
+      </c>
+      <c r="FF7" t="n">
+        <v>0.01063437107950449</v>
+      </c>
+      <c r="FG7" t="n">
+        <v>0.005037693306803703</v>
+      </c>
+      <c r="FH7" t="n">
+        <v>0.2360890805721283</v>
+      </c>
+      <c r="FI7" t="n">
+        <v>0.1023169308900833</v>
+      </c>
+      <c r="FJ7" t="n">
+        <v>0.03140533342957497</v>
+      </c>
+      <c r="FK7" t="n">
+        <v>0.08127040416002274</v>
+      </c>
+      <c r="FL7" t="n">
+        <v>0.1927638351917267</v>
+      </c>
+      <c r="FM7" t="n">
+        <v>0.08414578437805176</v>
+      </c>
+      <c r="FN7" t="n">
+        <v>0.338309109210968</v>
+      </c>
+      <c r="FO7" t="n">
+        <v>0.01029377058148384</v>
+      </c>
+      <c r="FP7" t="n">
+        <v>0.1214353814721107</v>
+      </c>
+      <c r="FQ7" t="n">
+        <v>0.1749357581138611</v>
+      </c>
+      <c r="FR7" t="n">
+        <v>0.3238978385925293</v>
+      </c>
+      <c r="FS7" t="n">
+        <v>0.2400347292423248</v>
+      </c>
+      <c r="FT7" t="n">
+        <v>0.05886097252368927</v>
+      </c>
+      <c r="FU7" t="n">
+        <v>0.2033778131008148</v>
+      </c>
+      <c r="FV7" t="n">
+        <v>0.1009543761610985</v>
+      </c>
+      <c r="FW7" t="n">
+        <v>0.00746864452958107</v>
+      </c>
+      <c r="FX7" t="n">
+        <v>0.04790191724896431</v>
+      </c>
+      <c r="FY7" t="n">
+        <v>0.0687871128320694</v>
+      </c>
+      <c r="FZ7" t="n">
+        <v>0.08567003905773163</v>
+      </c>
+      <c r="GA7" t="n">
+        <v>0.05872881785035133</v>
+      </c>
+      <c r="GB7" t="n">
+        <v>0.08203263580799103</v>
+      </c>
+      <c r="GC7" t="n">
+        <v>0.1616073846817017</v>
+      </c>
+      <c r="GD7" t="n">
+        <v>0.09503389894962311</v>
+      </c>
+      <c r="GE7" t="n">
+        <v>0.004831010475754738</v>
+      </c>
+      <c r="GF7" t="n">
+        <v>0.131237581372261</v>
+      </c>
+      <c r="GG7" t="n">
+        <v>0.1951426714658737</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0.0008260436006821692</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.002221533330157399</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.581008058972657e-05</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.000717008369974792</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0002182314783567563</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0008295701118186116</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0002344287931919098</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0006051153177395463</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0001084384130081162</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0005195307312533259</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.002399628749117255</v>
+      </c>
+      <c r="L9" t="n">
+        <v>9.491865057498217e-06</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0009945215424522758</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.0006793619832023978</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.001051084254868329</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.626800076337531e-05</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.0001686868345132098</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.0006639724597334862</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.0001684536400716752</v>
+      </c>
+      <c r="T9" t="n">
+        <v>6.012359517626464e-05</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.0001450427662348375</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.0003162314824294299</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.0004494158201850951</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.0003457770799286664</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.0002809436700772494</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.0004369368543848395</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>5.854043047293089e-05</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.00016080129717011</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>4.052725853398442e-05</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.0001866366364993155</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.0007066182442940772</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.00100701441988349</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.0004246705211699009</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.0001140002132160589</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.0006137959426268935</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.848737520049326e-05</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.0002503896539565176</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.0004403948551043868</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.0002712977875489742</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0.00033748839632608</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>8.4860366769135e-06</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0.0001846136874519289</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0.0003754647332243621</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0.0001831177942221984</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>8.651894313516095e-05</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0.0004538943467196077</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.001548255211673677</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0.0003194789169356227</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>2.596927333797794e-05</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0.001071436563506722</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0.0006145296501927078</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>2.745691381278448e-05</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0.0002411986788501963</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0.0002565612376201898</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0.0002527541073504835</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0.0004426940868142992</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0.000188289413927123</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0.000456280104117468</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0.000568972434848547</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0.000114213558845222</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>1.871739732450806e-05</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0.0002838771615643054</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0.0001456401951145381</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>6.857370317447931e-05</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0.000157173431944102</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>8.624216570751742e-05</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>3.917702997568995e-07</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0.0003615552559494972</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>2.625296474434435e-06</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0.0005200018058530986</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0.0002228919620392844</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0.0003628727863542736</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0.0003046308120246977</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0.001040008501149714</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0.000162073876708746</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>0.0001573405170347542</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>0.0002186849742429331</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0.0006770365289412439</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>0.0003214654861949384</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>6.813558866269886e-05</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0.0001420479093212634</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>0.0001826906373025849</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>0.0006473019020631909</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>6.443759048124775e-05</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0.0001936731132445857</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>0.0001123329493566416</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>0.0002732149150688201</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>0.0001113089165301062</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>9.964605851564556e-05</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>0.000162112875841558</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>0.0004103961400687695</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>0.0008573223021812737</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>0.0005024019628763199</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>0.0004493106389418244</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>5.722478090319782e-05</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>0.0004820706963073462</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>8.68580536916852e-05</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>0.0001660001289565116</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>0.0001831323024816811</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>9.732926992001012e-05</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>0.0006000623106956482</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>4.528007411863655e-05</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>0.0001938229106599465</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>0.000132822257000953</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>0.0002920413971878588</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>6.297853360592853e-06</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>0.0002339846978429705</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>0.0001220087797264569</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>0.0002299108600709587</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>0.0002658526645973325</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>0.000142335906275548</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>0.0003196954785380512</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>0.0008241867180913687</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>5.088222678750753e-05</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>0.0002201802853960544</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0.0001141201355494559</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>5.061426782049239e-05</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>0.0001423608046025038</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>0.0004281594301573932</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>0.000192858453374356</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>2.916971970989835e-05</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>0.0002869597519747913</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>0.0001932776212925091</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>0.0001999779487960041</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>0.0003941270406357944</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>0.0001897269103210419</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>0.0003001746081281453</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>0.0001922018855111673</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>0.0002823137037921697</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>0.0003543207421898842</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>9.110434621106833e-05</v>
+      </c>
+      <c r="EB9" t="n">
+        <v>2.172874519601464e-05</v>
+      </c>
+      <c r="EC9" t="n">
+        <v>7.397662557195872e-06</v>
+      </c>
+      <c r="ED9" t="n">
+        <v>0.0003287805011495948</v>
+      </c>
+      <c r="EE9" t="n">
+        <v>0.0002129381173290312</v>
+      </c>
+      <c r="EF9" t="n">
+        <v>2.411778405075893e-05</v>
+      </c>
+      <c r="EG9" t="n">
+        <v>0.0001539853401482105</v>
+      </c>
+      <c r="EH9" t="n">
+        <v>0.0003023151657544076</v>
+      </c>
+      <c r="EI9" t="n">
+        <v>2.67494579020422e-05</v>
+      </c>
+      <c r="EJ9" t="n">
+        <v>1.259476630366407e-05</v>
+      </c>
+      <c r="EK9" t="n">
+        <v>0.0001502551167504862</v>
+      </c>
+      <c r="EL9" t="n">
+        <v>5.794453318230808e-05</v>
+      </c>
+      <c r="EM9" t="n">
+        <v>0.0001935969048645347</v>
+      </c>
+      <c r="EN9" t="n">
+        <v>7.627339073223993e-05</v>
+      </c>
+      <c r="EO9" t="n">
+        <v>0.0002919920661952347</v>
+      </c>
+      <c r="EP9" t="n">
+        <v>0.000357292388798669</v>
+      </c>
+      <c r="EQ9" t="n">
+        <v>0.000110338005470112</v>
+      </c>
+      <c r="ER9" t="n">
+        <v>1.151441392721608e-05</v>
+      </c>
+      <c r="ES9" t="n">
+        <v>0.0002389473374933004</v>
+      </c>
+      <c r="ET9" t="n">
+        <v>0.0004171877517364919</v>
+      </c>
+      <c r="EU9" t="n">
+        <v>0.0001367878139717504</v>
+      </c>
+      <c r="EV9" t="n">
+        <v>9.333822526969016e-05</v>
+      </c>
+      <c r="EW9" t="n">
+        <v>0.0002235402789665386</v>
+      </c>
+      <c r="EX9" t="n">
+        <v>0.0001781889295671135</v>
+      </c>
+      <c r="EY9" t="n">
+        <v>0.0007092293817549944</v>
+      </c>
+      <c r="EZ9" t="n">
+        <v>4.128343425691128e-05</v>
+      </c>
+      <c r="FA9" t="n">
+        <v>0.0002257156738778576</v>
+      </c>
+      <c r="FB9" t="n">
+        <v>5.769704148406163e-05</v>
+      </c>
+      <c r="FC9" t="n">
+        <v>0.0002307532558916137</v>
+      </c>
+      <c r="FD9" t="n">
+        <v>0.0001171651674667373</v>
+      </c>
+      <c r="FE9" t="n">
+        <v>0.0001551485620439053</v>
+      </c>
+      <c r="FF9" t="n">
+        <v>2.114962990162894e-05</v>
+      </c>
+      <c r="FG9" t="n">
+        <v>3.90623026760295e-05</v>
+      </c>
+      <c r="FH9" t="n">
+        <v>0.0004440981429070234</v>
+      </c>
+      <c r="FI9" t="n">
+        <v>0.000317199039272964</v>
+      </c>
+      <c r="FJ9" t="n">
+        <v>0.0002313187578693032</v>
+      </c>
+      <c r="FK9" t="n">
+        <v>2.235058491351083e-05</v>
+      </c>
+      <c r="FL9" t="n">
+        <v>0.0004583770642057061</v>
+      </c>
+      <c r="FM9" t="n">
+        <v>0.0002138889103662223</v>
+      </c>
+      <c r="FN9" t="n">
+        <v>0.000281177053693682</v>
+      </c>
+      <c r="FO9" t="n">
+        <v>0.0004335993726272136</v>
+      </c>
+      <c r="FP9" t="n">
+        <v>0.0005272391717880964</v>
+      </c>
+      <c r="FQ9" t="n">
+        <v>0.0007926425896584988</v>
+      </c>
+      <c r="FR9" t="n">
+        <v>0.000482436444144696</v>
+      </c>
+      <c r="FS9" t="n">
+        <v>0.0005147329648025334</v>
+      </c>
+      <c r="FT9" t="n">
+        <v>0.0001184341963380575</v>
+      </c>
+      <c r="FU9" t="n">
+        <v>0.0004972799797542393</v>
+      </c>
+      <c r="FV9" t="n">
+        <v>0.0003192313306499273</v>
+      </c>
+      <c r="FW9" t="n">
+        <v>0.0001882825163193047</v>
+      </c>
+      <c r="FX9" t="n">
+        <v>0.0001360929454676807</v>
+      </c>
+      <c r="FY9" t="n">
+        <v>0.0002617259160615504</v>
+      </c>
+      <c r="FZ9" t="n">
+        <v>4.657777753891423e-05</v>
+      </c>
+      <c r="GA9" t="n">
+        <v>0.0003334850480314344</v>
+      </c>
+      <c r="GB9" t="n">
+        <v>9.823806612985209e-05</v>
+      </c>
+      <c r="GC9" t="n">
+        <v>5.181979213375598e-05</v>
+      </c>
+      <c r="GD9" t="n">
+        <v>0.0004576920182444155</v>
+      </c>
+      <c r="GE9" t="n">
+        <v>0.0003244426043238491</v>
+      </c>
+      <c r="GF9" t="n">
+        <v>0.0002494744258001447</v>
+      </c>
+      <c r="GG9" t="n">
+        <v>0.0001646796154091135</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>0</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>0.01019753143191338</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.0238927286118269</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.006440467666834593</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.006175252143293619</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.008439410477876663</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.05464399233460426</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.002081149257719517</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.04950248077511787</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.008190939202904701</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.008727054111659527</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.02442037686705589</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.001754708355292678</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.01383065432310104</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.001930044963955879</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.04915768653154373</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.008872362785041332</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.05822572112083435</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.01896366849541664</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.001756012788973749</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.00781055074185133</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.002516899956390262</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.01190989464521408</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.004189717117697001</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.002312871161848307</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.001547556254081428</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.004827135242521763</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.002378985751420259</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.001489729387685657</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.002050310140475631</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.003659685142338276</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.02198026701807976</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.02865820378065109</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.001133357407525182</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.01609085500240326</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.003854142501950264</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.008365425281226635</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.003095971420407295</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.009256746619939804</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.008495057001709938</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0.0007836490403860807</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.01976414769887924</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0.02268329076468945</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0.006784086115658283</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0.003651005914434791</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0.005910542327910662</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0.0006890548393130302</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0.06214817613363266</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.005101587623357773</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.003045990131795406</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0.02386035770177841</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0.02132440730929375</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.005623181350529194</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0.0004263615701347589</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0.01612578332424164</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0.00369202671572566</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0.04374512284994125</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0.01215062569826841</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0.004886164795607328</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0.05498028546571732</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0.0100103784352541</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>0.005588424392044544</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0.004597917199134827</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0.00117582269012928</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0.005589007865637541</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.0001775235868990421</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>0.01599747128784657</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0.003367481753230095</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>0.004408129490911961</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>0.006181560456752777</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>0.004081880208104849</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>0.01083298400044441</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>6.467453204095364e-05</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>0.0001094560138881207</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>0.02770108357071877</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>0.0009023742750287056</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>0.00590844452381134</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>0.01181676611304283</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>0.02058239281177521</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>0.005655601620674133</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>0.003243026789277792</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>0.001537800533697009</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>0.00167339516337961</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>0.009838567115366459</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>0.007926177233457565</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>0.004003117326647043</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>0.002716126618906856</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>0.01521154493093491</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>0.002378481905907393</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>0.01128647848963737</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>0.003896828275173903</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>0.003315014066174626</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>0.00429469533264637</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>0.01201480254530907</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>0.02105741761624813</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>0.04842180013656616</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>0.007326327264308929</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>0.008134417235851288</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>0.01828761398792267</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>0.003168945200741291</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>0.001237130025401711</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>0.007278884761035442</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>0.005984821822494268</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>0.002611675765365362</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>0.002317133825272322</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>0.01568069495260715</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>0.000600203056819737</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>0.007229621522128582</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>0.002612030133605003</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>0.01456733513623476</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>0.02076741307973862</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>0.00924014113843441</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>0.01605778187513351</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>0.01956150121986866</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>0.01015442050993443</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>0.0130133181810379</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>0.003267751773819327</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>0.02857598103582859</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>0.005846352782100439</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>0.004334372468292713</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>6.156181916594505e-05</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>0.007065135985612869</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>0.002508220262825489</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>0.008169367909431458</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>0.003779669292271137</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>0.00294588366523385</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>0.0007590855821035802</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>0.0003196411998942494</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>0.002852421486750245</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>0.01184536889195442</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>0.01307336799800396</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>0.003754973877221346</v>
+      </c>
+      <c r="EB11" t="n">
+        <v>0.00194945465773344</v>
+      </c>
+      <c r="EC11" t="n">
+        <v>0.005464504007250071</v>
+      </c>
+      <c r="ED11" t="n">
+        <v>0.003763569518923759</v>
+      </c>
+      <c r="EE11" t="n">
+        <v>0.01571465469896793</v>
+      </c>
+      <c r="EF11" t="n">
+        <v>0.003014311892911792</v>
+      </c>
+      <c r="EG11" t="n">
+        <v>5.065719597041607e-05</v>
+      </c>
+      <c r="EH11" t="n">
+        <v>0.00352317956276238</v>
+      </c>
+      <c r="EI11" t="n">
+        <v>0.004815438762307167</v>
+      </c>
+      <c r="EJ11" t="n">
+        <v>0.007559666875749826</v>
+      </c>
+      <c r="EK11" t="n">
+        <v>0.0006380492122843862</v>
+      </c>
+      <c r="EL11" t="n">
+        <v>0.009459859691560268</v>
+      </c>
+      <c r="EM11" t="n">
+        <v>0.01157130487263203</v>
+      </c>
+      <c r="EN11" t="n">
+        <v>0.003576491959393024</v>
+      </c>
+      <c r="EO11" t="n">
+        <v>0.002901877742260695</v>
+      </c>
+      <c r="EP11" t="n">
+        <v>0.01483710668981075</v>
+      </c>
+      <c r="EQ11" t="n">
+        <v>6.941740866750479e-05</v>
+      </c>
+      <c r="ER11" t="n">
+        <v>0.00590863823890686</v>
+      </c>
+      <c r="ES11" t="n">
+        <v>0.008511775173246861</v>
+      </c>
+      <c r="ET11" t="n">
+        <v>0.01832576282322407</v>
+      </c>
+      <c r="EU11" t="n">
+        <v>0.02106642536818981</v>
+      </c>
+      <c r="EV11" t="n">
+        <v>0.009528441354632378</v>
+      </c>
+      <c r="EW11" t="n">
+        <v>0.0117780789732933</v>
+      </c>
+      <c r="EX11" t="n">
+        <v>0.0003428782802075148</v>
+      </c>
+      <c r="EY11" t="n">
+        <v>0.01071758754551411</v>
+      </c>
+      <c r="EZ11" t="n">
+        <v>0.006304137408733368</v>
+      </c>
+      <c r="FA11" t="n">
+        <v>0.002293504541739821</v>
+      </c>
+      <c r="FB11" t="n">
+        <v>0.001216418109834194</v>
+      </c>
+      <c r="FC11" t="n">
+        <v>0.01312777400016785</v>
+      </c>
+      <c r="FD11" t="n">
+        <v>0.001580022042617202</v>
+      </c>
+      <c r="FE11" t="n">
+        <v>0.009058913215994835</v>
+      </c>
+      <c r="FF11" t="n">
+        <v>0.0003838440170511603</v>
+      </c>
+      <c r="FG11" t="n">
+        <v>0.00304695894010365</v>
+      </c>
+      <c r="FH11" t="n">
+        <v>0.01581935025751591</v>
+      </c>
+      <c r="FI11" t="n">
+        <v>0.001945454394444823</v>
+      </c>
+      <c r="FJ11" t="n">
+        <v>0.00597029784694314</v>
+      </c>
+      <c r="FK11" t="n">
+        <v>0.002123076934367418</v>
+      </c>
+      <c r="FL11" t="n">
+        <v>0.01676136255264282</v>
+      </c>
+      <c r="FM11" t="n">
+        <v>0.003807255998253822</v>
+      </c>
+      <c r="FN11" t="n">
+        <v>0.003470940282568336</v>
+      </c>
+      <c r="FO11" t="n">
+        <v>5.955807864665985e-07</v>
+      </c>
+      <c r="FP11" t="n">
+        <v>0.000205503311008215</v>
+      </c>
+      <c r="FQ11" t="n">
+        <v>0.03026409074664116</v>
+      </c>
+      <c r="FR11" t="n">
+        <v>0.04894767701625824</v>
+      </c>
+      <c r="FS11" t="n">
+        <v>0.01314764842391014</v>
+      </c>
+      <c r="FT11" t="n">
+        <v>0.007646081037819386</v>
+      </c>
+      <c r="FU11" t="n">
+        <v>0.02493723668158054</v>
+      </c>
+      <c r="FV11" t="n">
+        <v>0.01639064401388168</v>
+      </c>
+      <c r="FW11" t="n">
+        <v>0.006610164884477854</v>
+      </c>
+      <c r="FX11" t="n">
+        <v>0.03136305138468742</v>
+      </c>
+      <c r="FY11" t="n">
+        <v>0.0109718069434166</v>
+      </c>
+      <c r="FZ11" t="n">
+        <v>0.006216810550540686</v>
+      </c>
+      <c r="GA11" t="n">
+        <v>0.001947846263647079</v>
+      </c>
+      <c r="GB11" t="n">
+        <v>0.005636535584926605</v>
+      </c>
+      <c r="GC11" t="n">
+        <v>0.008750095963478088</v>
+      </c>
+      <c r="GD11" t="n">
+        <v>0.001170734176412225</v>
+      </c>
+      <c r="GE11" t="n">
+        <v>0.001924865297041833</v>
+      </c>
+      <c r="GF11" t="n">
+        <v>0.0122876837849617</v>
+      </c>
+      <c r="GG11" t="n">
+        <v>0.006713860668241978</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>4.445590207069472e-07</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2.644445339683443e-05</v>
+      </c>
+      <c r="C12" t="n">
+        <v>9.225758731190581e-06</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4.493820597417653e-06</v>
+      </c>
+      <c r="E12" t="n">
+        <v>6.811857019783929e-06</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.55190552707063e-05</v>
+      </c>
+      <c r="G12" t="n">
+        <v>4.335964831625461e-07</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.400241853843909e-05</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.242013690396561e-06</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.449787987439777e-06</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.311540058348328e-05</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.463290573155973e-05</v>
+      </c>
+      <c r="M12" t="n">
+        <v>9.639119525672868e-06</v>
+      </c>
+      <c r="N12" t="n">
+        <v>7.211975116661051e-06</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.614634831843432e-05</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.680731995496899e-06</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.195153163280338e-05</v>
+      </c>
+      <c r="R12" t="n">
+        <v>3.038858039872139e-06</v>
+      </c>
+      <c r="S12" t="n">
+        <v>6.194645720825065e-07</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.431544999126345e-06</v>
+      </c>
+      <c r="U12" t="n">
+        <v>5.536662683880422e-07</v>
+      </c>
+      <c r="V12" t="n">
+        <v>3.964681582147023e-06</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.430003860354191e-06</v>
+      </c>
+      <c r="X12" t="n">
+        <v>8.868670192896388e-06</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.097069454976008e-06</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4.530080332187936e-06</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>6.99853444530163e-07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.914761924126651e-06</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.96277698907943e-06</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2.595915702841012e-06</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>3.296162503829692e-06</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>6.797438345529372e-06</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>5.666532160830684e-06</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>2.14926467378973e-06</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1.30893558889511e-05</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>3.325073294035974e-06</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>2.297525043104542e-06</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>7.309041393455118e-06</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.295619313168572e-06</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>4.960032129019964e-06</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1.2779739790858e-06</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>3.682057467813138e-06</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>5.436090759758372e-07</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>5.720055014535319e-06</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>3.688203378260368e-06</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>4.434776656125905e-06</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>3.221602673875168e-05</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>3.886232207150897e-06</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>4.556280146061908e-06</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.388506734656403e-05</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>2.187250174756628e-05</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.035681066241523e-06</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>3.415016863073106e-06</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>3.661949904198991e-06</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1.433811803508434e-06</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>7.908134648459964e-06</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>6.649388069490669e-06</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>1.893630496851983e-07</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>9.97767347143963e-06</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>1.831048621170339e-06</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>4.441040346137015e-06</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>3.503020707285032e-06</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>4.704267666966189e-06</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1.642593019823835e-06</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>3.511416025503422e-06</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>1.729619270918192e-06</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>2.830420271493495e-07</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>1.423793833055242e-06</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>1.688828660917352e-06</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>3.241257218178362e-07</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>6.168432946651592e-07</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>2.410036358924117e-06</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>1.234115416082204e-06</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>1.615399014553986e-05</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>1.430296833859757e-06</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>4.859174623561557e-06</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>5.725425126001937e-06</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>1.49632578541059e-05</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>4.074834123457549e-06</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>3.688810465973802e-06</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>5.329725354386028e-07</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>6.024939125381934e-07</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>9.732205398904625e-06</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>1.75494062659709e-06</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>2.701689709283528e-06</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>5.779859293397749e-07</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>5.796356617793208e-06</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>1.234771360714149e-07</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>2.877003225876251e-06</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>8.495507017869386e-07</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>2.841805780917639e-06</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>6.980475518503226e-06</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>6.931591087777633e-06</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>7.040184755169321e-06</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>9.041422345035244e-06</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>4.78860374641954e-06</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>7.649476856386173e-07</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>7.195828288786288e-07</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>3.00715328194201e-06</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>1.082713652067469e-06</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>8.451413123111706e-06</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>3.092490715062013e-06</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>4.011982582596829e-06</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>1.347175498267461e-06</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>6.831332939327694e-06</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>1.000317297439324e-06</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>2.149382908100961e-06</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>1.62058725550196e-07</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>2.642591425683349e-07</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>6.826221579103731e-06</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>3.349745838931995e-06</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>1.588388158779708e-06</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>1.06456468529359e-06</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>1.060508566297358e-05</v>
+      </c>
+      <c r="DK12" t="n">
+        <v>1.480658056607354e-06</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>1.081714162864955e-05</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>4.034172889078036e-06</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>2.092732529490604e-06</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>3.389000539755216e-06</v>
+      </c>
+      <c r="DP12" t="n">
+        <v>1.681240519246785e-06</v>
+      </c>
+      <c r="DQ12" t="n">
+        <v>8.410183340856747e-07</v>
+      </c>
+      <c r="DR12" t="n">
+        <v>8.716391448615468e-07</v>
+      </c>
+      <c r="DS12" t="n">
+        <v>5.041278200224042e-06</v>
+      </c>
+      <c r="DT12" t="n">
+        <v>3.782784915529191e-06</v>
+      </c>
+      <c r="DU12" t="n">
+        <v>6.258235771383625e-06</v>
+      </c>
+      <c r="DV12" t="n">
+        <v>5.594021672550298e-07</v>
+      </c>
+      <c r="DW12" t="n">
+        <v>4.799862381332787e-06</v>
+      </c>
+      <c r="DX12" t="n">
+        <v>5.235822754912078e-06</v>
+      </c>
+      <c r="DY12" t="n">
+        <v>5.275238891044864e-06</v>
+      </c>
+      <c r="DZ12" t="n">
+        <v>9.692408866612823e-07</v>
+      </c>
+      <c r="EA12" t="n">
+        <v>5.333396529749734e-06</v>
+      </c>
+      <c r="EB12" t="n">
+        <v>7.042780453048181e-06</v>
+      </c>
+      <c r="EC12" t="n">
+        <v>2.981850684591336e-06</v>
+      </c>
+      <c r="ED12" t="n">
+        <v>8.344050911546219e-06</v>
+      </c>
+      <c r="EE12" t="n">
+        <v>6.977083558012964e-06</v>
+      </c>
+      <c r="EF12" t="n">
+        <v>1.923799345604493e-06</v>
+      </c>
+      <c r="EG12" t="n">
+        <v>4.453319888853002e-06</v>
+      </c>
+      <c r="EH12" t="n">
+        <v>8.922368124331115e-07</v>
+      </c>
+      <c r="EI12" t="n">
+        <v>7.13920144335134e-07</v>
+      </c>
+      <c r="EJ12" t="n">
+        <v>2.205969849455869e-06</v>
+      </c>
+      <c r="EK12" t="n">
+        <v>2.202726591349347e-06</v>
+      </c>
+      <c r="EL12" t="n">
+        <v>1.388685859637917e-06</v>
+      </c>
+      <c r="EM12" t="n">
+        <v>1.761909175002074e-06</v>
+      </c>
+      <c r="EN12" t="n">
+        <v>8.585150794715446e-07</v>
+      </c>
+      <c r="EO12" t="n">
+        <v>2.594386387499981e-06</v>
+      </c>
+      <c r="EP12" t="n">
+        <v>4.09693438996328e-06</v>
+      </c>
+      <c r="EQ12" t="n">
+        <v>4.806861966244469e-07</v>
+      </c>
+      <c r="ER12" t="n">
+        <v>5.47224044566974e-06</v>
+      </c>
+      <c r="ES12" t="n">
+        <v>3.457760612946004e-06</v>
+      </c>
+      <c r="ET12" t="n">
+        <v>6.89752937432786e-07</v>
+      </c>
+      <c r="EU12" t="n">
+        <v>5.436943979475473e-07</v>
+      </c>
+      <c r="EV12" t="n">
+        <v>2.206657200076734e-06</v>
+      </c>
+      <c r="EW12" t="n">
+        <v>4.668816018238431e-06</v>
+      </c>
+      <c r="EX12" t="n">
+        <v>5.118614581078873e-07</v>
+      </c>
+      <c r="EY12" t="n">
+        <v>1.046854413289111e-05</v>
+      </c>
+      <c r="EZ12" t="n">
+        <v>2.182964180974523e-06</v>
+      </c>
+      <c r="FA12" t="n">
+        <v>3.309855401312234e-06</v>
+      </c>
+      <c r="FB12" t="n">
+        <v>2.299760808455176e-07</v>
+      </c>
+      <c r="FC12" t="n">
+        <v>7.056484719214495e-06</v>
+      </c>
+      <c r="FD12" t="n">
+        <v>3.276143161201617e-07</v>
+      </c>
+      <c r="FE12" t="n">
+        <v>2.829310915331007e-06</v>
+      </c>
+      <c r="FF12" t="n">
+        <v>1.165321123153262e-06</v>
+      </c>
+      <c r="FG12" t="n">
+        <v>1.559236807224806e-06</v>
+      </c>
+      <c r="FH12" t="n">
+        <v>6.093012416386046e-06</v>
+      </c>
+      <c r="FI12" t="n">
+        <v>3.076694838455296e-06</v>
+      </c>
+      <c r="FJ12" t="n">
+        <v>2.116858013323508e-06</v>
+      </c>
+      <c r="FK12" t="n">
+        <v>2.778554289761814e-06</v>
+      </c>
+      <c r="FL12" t="n">
+        <v>3.625767021731008e-06</v>
+      </c>
+      <c r="FM12" t="n">
+        <v>1.2764351140504e-06</v>
+      </c>
+      <c r="FN12" t="n">
+        <v>8.003768925846089e-06</v>
+      </c>
+      <c r="FO12" t="n">
+        <v>8.336000973940827e-06</v>
+      </c>
+      <c r="FP12" t="n">
+        <v>2.74438934866339e-06</v>
+      </c>
+      <c r="FQ12" t="n">
+        <v>4.240105681674322e-06</v>
+      </c>
+      <c r="FR12" t="n">
+        <v>7.350499799940735e-06</v>
+      </c>
+      <c r="FS12" t="n">
+        <v>1.503318003415188e-06</v>
+      </c>
+      <c r="FT12" t="n">
+        <v>3.137374733341858e-06</v>
+      </c>
+      <c r="FU12" t="n">
+        <v>4.058707872900413e-06</v>
+      </c>
+      <c r="FV12" t="n">
+        <v>7.376954272331204e-06</v>
+      </c>
+      <c r="FW12" t="n">
+        <v>1.077991237252718e-05</v>
+      </c>
+      <c r="FX12" t="n">
+        <v>7.08402967575239e-06</v>
+      </c>
+      <c r="FY12" t="n">
+        <v>2.827131993399234e-06</v>
+      </c>
+      <c r="FZ12" t="n">
+        <v>3.798587613346172e-07</v>
+      </c>
+      <c r="GA12" t="n">
+        <v>8.525084922439419e-06</v>
+      </c>
+      <c r="GB12" t="n">
+        <v>6.659125233454688e-07</v>
+      </c>
+      <c r="GC12" t="n">
+        <v>1.031344709190307e-05</v>
+      </c>
+      <c r="GD12" t="n">
+        <v>6.314468009804841e-06</v>
+      </c>
+      <c r="GE12" t="n">
+        <v>2.201643383159535e-06</v>
+      </c>
+      <c r="GF12" t="n">
+        <v>2.476517920513288e-06</v>
+      </c>
+      <c r="GG12" t="n">
+        <v>2.871996912290342e-06</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>0.002622077241539955</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.2486110925674438</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.1335588395595551</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.0371357835829258</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.01498771086335182</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.1053254455327988</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.04946509748697281</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.01173576712608337</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.1825170964002609</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.01352476142346859</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.2677792906761169</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.1411073505878448</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.0216915886849165</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.07684844732284546</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.08778755366802216</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.06057462841272354</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.05160620808601379</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.1502238810062408</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.004106749780476093</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.05312735959887505</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.05209127813577652</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.007905274629592896</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.01022235956043005</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.06292697042226791</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.01401375606656075</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.003270439337939024</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.07273036241531372</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.06694035977125168</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.02190567180514336</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.0003608483821153641</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.1136544123291969</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.1348745226860046</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.03550994396209717</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0.02529584802687168</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.002804928459227085</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.113152913749218</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0.01210577785968781</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.08663472533226013</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0.006962865591049194</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0.03241619467735291</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.14100082218647</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0.04921639710664749</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0.001864994876086712</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0.01162919402122498</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0.01866233348846436</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0.02734344452619553</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0.2035261690616608</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0.03136608004570007</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.06547801196575165</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0.02322639152407646</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0.118965819478035</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.01024108845740557</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0.05068421363830566</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0.09026359021663666</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0.03573048114776611</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0.03857601806521416</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0.08645717799663544</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0.04099735617637634</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0.06554944068193436</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0.05664309114217758</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>0.03104026429355145</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0.0103723555803299</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0.03429399058222771</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0.01913082040846348</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0.05541936308145523</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>0.01678700000047684</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0.0827869176864624</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>0.002065397799015045</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0.01441464107483625</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>0.02209166064858437</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>0.02854344993829727</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>0.03521639853715897</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>0.01739443838596344</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>0.1126040369272232</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>0.00560611579567194</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>0.007504234090447426</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>0.01883690990507603</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>0.09249348193407059</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>0.004670171067118645</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>0.005713927559554577</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>0.08469586819410324</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>0.007239098660647869</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>0.09940881282091141</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>0.04736481234431267</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>0.01323886401951313</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>0.01111798919737339</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>0.01560603268444538</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>0.0003696158528327942</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>0.009946884587407112</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>0.03552554547786713</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>0.02020561136305332</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>0.1123999357223511</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>0.0463913232088089</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>0.1119881272315979</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>0.1057923808693886</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>0.144063875079155</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>0.01060496736317873</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>0.0008427519351243973</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>0.007539710029959679</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>0.01525998674333096</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>0.1016577631235123</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>0.05105588212609291</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>0.01327368896454573</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>0.003534628544002771</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>0.02991913259029388</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>0.007898995652794838</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>0.007814523763954639</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>0.05835898220539093</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>0.02292376384139061</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>0.1275382488965988</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>0.08287834376096725</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>0.0160987600684166</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>0.03979962319135666</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>0.0529363751411438</v>
+      </c>
+      <c r="DK13" t="n">
+        <v>0.006875633262097836</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>0.02480794675648212</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>0.1193285882472992</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>0.03760345280170441</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>0.01890329644083977</v>
+      </c>
+      <c r="DP13" t="n">
+        <v>0.05570563301444054</v>
+      </c>
+      <c r="DQ13" t="n">
+        <v>0.02802644483745098</v>
+      </c>
+      <c r="DR13" t="n">
+        <v>0.03493231907486916</v>
+      </c>
+      <c r="DS13" t="n">
+        <v>0.01328183710575104</v>
+      </c>
+      <c r="DT13" t="n">
+        <v>0.02554973214864731</v>
+      </c>
+      <c r="DU13" t="n">
+        <v>0.004382525570690632</v>
+      </c>
+      <c r="DV13" t="n">
+        <v>0.04676027223467827</v>
+      </c>
+      <c r="DW13" t="n">
+        <v>0.005747116636484861</v>
+      </c>
+      <c r="DX13" t="n">
+        <v>0.04425674676895142</v>
+      </c>
+      <c r="DY13" t="n">
+        <v>0.05002229288220406</v>
+      </c>
+      <c r="DZ13" t="n">
+        <v>0.01030700094997883</v>
+      </c>
+      <c r="EA13" t="n">
+        <v>0.01119913998991251</v>
+      </c>
+      <c r="EB13" t="n">
+        <v>0.1071233525872231</v>
+      </c>
+      <c r="EC13" t="n">
+        <v>0.005241705104708672</v>
+      </c>
+      <c r="ED13" t="n">
+        <v>0.04392541199922562</v>
+      </c>
+      <c r="EE13" t="n">
+        <v>0.05781657993793488</v>
+      </c>
+      <c r="EF13" t="n">
+        <v>0.004939192906022072</v>
+      </c>
+      <c r="EG13" t="n">
+        <v>0.1137418448925018</v>
+      </c>
+      <c r="EH13" t="n">
+        <v>0.005021411925554276</v>
+      </c>
+      <c r="EI13" t="n">
+        <v>0.006500675342977047</v>
+      </c>
+      <c r="EJ13" t="n">
+        <v>0.01955710723996162</v>
+      </c>
+      <c r="EK13" t="n">
+        <v>0.03204137831926346</v>
+      </c>
+      <c r="EL13" t="n">
+        <v>0.01016498543322086</v>
+      </c>
+      <c r="EM13" t="n">
+        <v>0.006862998474389315</v>
+      </c>
+      <c r="EN13" t="n">
+        <v>0.05578659474849701</v>
+      </c>
+      <c r="EO13" t="n">
+        <v>0.01936308294534683</v>
+      </c>
+      <c r="EP13" t="n">
+        <v>0.05440285056829453</v>
+      </c>
+      <c r="EQ13" t="n">
+        <v>0.001251286827027798</v>
+      </c>
+      <c r="ER13" t="n">
+        <v>0.005828684195876122</v>
+      </c>
+      <c r="ES13" t="n">
+        <v>0.01026407163590193</v>
+      </c>
+      <c r="ET13" t="n">
+        <v>0.01008625421673059</v>
+      </c>
+      <c r="EU13" t="n">
+        <v>0.0260743536055088</v>
+      </c>
+      <c r="EV13" t="n">
+        <v>0.0267214048653841</v>
+      </c>
+      <c r="EW13" t="n">
+        <v>0.02499599754810333</v>
+      </c>
+      <c r="EX13" t="n">
+        <v>0.008598968386650085</v>
+      </c>
+      <c r="EY13" t="n">
+        <v>0.1105989441275597</v>
+      </c>
+      <c r="EZ13" t="n">
+        <v>0.05176401883363724</v>
+      </c>
+      <c r="FA13" t="n">
+        <v>0.02376847714185715</v>
+      </c>
+      <c r="FB13" t="n">
+        <v>0.01026598270982504</v>
+      </c>
+      <c r="FC13" t="n">
+        <v>0.02801614813506603</v>
+      </c>
+      <c r="FD13" t="n">
+        <v>0.002161514014005661</v>
+      </c>
+      <c r="FE13" t="n">
+        <v>0.00399906886741519</v>
+      </c>
+      <c r="FF13" t="n">
+        <v>0.05420032888650894</v>
+      </c>
+      <c r="FG13" t="n">
+        <v>0.01242983154952526</v>
+      </c>
+      <c r="FH13" t="n">
+        <v>0.05786030739545822</v>
+      </c>
+      <c r="FI13" t="n">
+        <v>0.02879513427615166</v>
+      </c>
+      <c r="FJ13" t="n">
+        <v>0.01781412959098816</v>
+      </c>
+      <c r="FK13" t="n">
+        <v>0.00333537720143795</v>
+      </c>
+      <c r="FL13" t="n">
+        <v>0.001957088708877563</v>
+      </c>
+      <c r="FM13" t="n">
+        <v>0.01207189448177814</v>
+      </c>
+      <c r="FN13" t="n">
+        <v>0.01964752748608589</v>
+      </c>
+      <c r="FO13" t="n">
+        <v>0.07080411911010742</v>
+      </c>
+      <c r="FP13" t="n">
+        <v>0.07453738152980804</v>
+      </c>
+      <c r="FQ13" t="n">
+        <v>0.11839859187603</v>
+      </c>
+      <c r="FR13" t="n">
+        <v>0.04325249418616295</v>
+      </c>
+      <c r="FS13" t="n">
+        <v>0.004347305744886398</v>
+      </c>
+      <c r="FT13" t="n">
+        <v>0.04163188859820366</v>
+      </c>
+      <c r="FU13" t="n">
+        <v>0.016710564494133</v>
+      </c>
+      <c r="FV13" t="n">
+        <v>0.02034800499677658</v>
+      </c>
+      <c r="FW13" t="n">
+        <v>0.07539971172809601</v>
+      </c>
+      <c r="FX13" t="n">
+        <v>0.07082237303256989</v>
+      </c>
+      <c r="FY13" t="n">
+        <v>0.01100025232881308</v>
+      </c>
+      <c r="FZ13" t="n">
+        <v>0.1035643219947815</v>
+      </c>
+      <c r="GA13" t="n">
+        <v>0.05243944376707077</v>
+      </c>
+      <c r="GB13" t="n">
+        <v>0.01037093997001648</v>
+      </c>
+      <c r="GC13" t="n">
+        <v>0.06025892496109009</v>
+      </c>
+      <c r="GD13" t="n">
+        <v>0.00224623829126358</v>
+      </c>
+      <c r="GE13" t="n">
+        <v>0.02828537113964558</v>
+      </c>
+      <c r="GF13" t="n">
+        <v>0.07165219634771347</v>
+      </c>
+      <c r="GG13" t="n">
+        <v>0.05329766497015953</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9.90417756838724e-05</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.001016155467368662</v>
+      </c>
+      <c r="C14" t="n">
+        <v>9.229860734194517e-05</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.0004767353821080178</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.000333216565195471</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.0008761611534282565</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.0004756704438477755</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.0007749556680209935</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.0001546000421512872</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.0001295583933824673</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.001199303078465164</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.0001446696842322126</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.0007411580299958587</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.0007497791084460914</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.001192367170006037</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.0003345804871059954</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.0004035554593428969</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.0002941233396995813</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.0001047362529789098</v>
+      </c>
+      <c r="T14" t="n">
+        <v>7.618300151079893e-05</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.00020587831386365</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.0001488000707468018</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.0001643738360144198</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.0002043783897534013</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.000125243968795985</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.0004538750217761844</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>5.690921534551308e-05</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.0002134796231985092</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.0001769335940480232</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.972115569515154e-05</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0.0003021008451469243</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.0001687636249698699</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.0003960671892855316</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>2.221762042609043e-05</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.0008630788652226329</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.0001165542926173657</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0.0001749207149259746</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>7.83747382229194e-05</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.0002193916880059987</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0.0001049224301823415</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0.0002035220677498728</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0.0001148018418462016</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>8.484023419441655e-05</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0.0004877686151303351</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>8.108253678074107e-05</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0.0003304718993604183</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0.0008386148838326335</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0.0002192101674154401</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0.0003265488485340029</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0.0008386177360080183</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0.0007071990403346717</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>2.189688530052081e-05</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0.0001594172790646553</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>9.457259147893637e-05</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>6.955189019208774e-05</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0.0004190174513496459</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>8.231087122112513e-05</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0.0003866491606459022</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0.0005075698718428612</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>0.0001096804262488149</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>0.0001426580420229584</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0.0007174364291131496</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>2.751768261077814e-05</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>3.381727219675668e-05</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0.0002584261819720268</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>4.05781865993049e-05</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>7.330509833991528e-05</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>0.0002059398830169812</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>2.217670771642588e-05</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>0.0005780745414085686</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>0.0002465319994371384</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>9.751458128448576e-05</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>0.0001524837862234563</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>0.0003187821712344885</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>0.0002146041806554422</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>0.0002179101720685139</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>0.0002927962632384151</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>0.0003516183060128242</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>0.0001326314377365634</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>0.0001369056117255241</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>2.568190029705875e-05</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>4.573430487653241e-05</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>0.0002968849730677903</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>1.603722012077924e-05</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>0.0001489066344220191</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>0.0001370062818750739</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>0.0002923175925388932</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>0.0001239473203895614</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>5.722796049667522e-05</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>9.839667472988367e-05</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>0.0001013608634821139</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>0.0004210320767015219</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>0.0005086094024591148</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>0.0006045045447535813</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>8.543232979718596e-06</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>0.0003290991007816046</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>0.0001198042373289354</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>0.0002750156272668391</v>
+      </c>
+      <c r="CU14" t="n">
+        <v>0.0002427303115837276</v>
+      </c>
+      <c r="CV14" t="n">
+        <v>9.167096141027287e-05</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>0.0002648408699315041</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>8.320699635078199e-06</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>0.0002068086032522842</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>9.852556831901893e-05</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>0.0003337033849675208</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>2.698706157389097e-05</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>2.956220669148024e-05</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>4.728881322080269e-05</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>0.0001355480053462088</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>0.0001124151604017243</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>0.0003463492321316153</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>0.0001039008202496916</v>
+      </c>
+      <c r="DI14" t="n">
+        <v>0.0006827293545939028</v>
+      </c>
+      <c r="DJ14" t="n">
+        <v>0.0002655638090800494</v>
+      </c>
+      <c r="DK14" t="n">
+        <v>0.0001404961221851408</v>
+      </c>
+      <c r="DL14" t="n">
+        <v>0.0004094642063137144</v>
+      </c>
+      <c r="DM14" t="n">
+        <v>0.0001966959971468896</v>
+      </c>
+      <c r="DN14" t="n">
+        <v>0.0001516791671747342</v>
+      </c>
+      <c r="DO14" t="n">
+        <v>0.0002015519130509347</v>
+      </c>
+      <c r="DP14" t="n">
+        <v>0.0001286217739107087</v>
+      </c>
+      <c r="DQ14" t="n">
+        <v>0.0001699243002803996</v>
+      </c>
+      <c r="DR14" t="n">
+        <v>2.907842281274498e-05</v>
+      </c>
+      <c r="DS14" t="n">
+        <v>1.245731800736394e-05</v>
+      </c>
+      <c r="DT14" t="n">
+        <v>0.0002308225666638464</v>
+      </c>
+      <c r="DU14" t="n">
+        <v>0.0004554574261419475</v>
+      </c>
+      <c r="DV14" t="n">
+        <v>0.0001048467456712388</v>
+      </c>
+      <c r="DW14" t="n">
+        <v>0.0001220591657329351</v>
+      </c>
+      <c r="DX14" t="n">
+        <v>0.000115629707579501</v>
+      </c>
+      <c r="DY14" t="n">
+        <v>4.206273661111481e-05</v>
+      </c>
+      <c r="DZ14" t="n">
+        <v>0.0003255006740801036</v>
+      </c>
+      <c r="EA14" t="n">
+        <v>0.0002669526729732752</v>
+      </c>
+      <c r="EB14" t="n">
+        <v>0.0001445445523131639</v>
+      </c>
+      <c r="EC14" t="n">
+        <v>3.611263673519716e-05</v>
+      </c>
+      <c r="ED14" t="n">
+        <v>0.0001685437164269388</v>
+      </c>
+      <c r="EE14" t="n">
+        <v>0.0004430643166415393</v>
+      </c>
+      <c r="EF14" t="n">
+        <v>2.403727376076858e-05</v>
+      </c>
+      <c r="EG14" t="n">
+        <v>0.0001133146288339049</v>
+      </c>
+      <c r="EH14" t="n">
+        <v>0.000113645481178537</v>
+      </c>
+      <c r="EI14" t="n">
+        <v>1.072721715900116e-05</v>
+      </c>
+      <c r="EJ14" t="n">
+        <v>0.0001334796252194792</v>
+      </c>
+      <c r="EK14" t="n">
+        <v>0.0003475053235888481</v>
+      </c>
+      <c r="EL14" t="n">
+        <v>0.0001277283299714327</v>
+      </c>
+      <c r="EM14" t="n">
+        <v>1.644206895434763e-05</v>
+      </c>
+      <c r="EN14" t="n">
+        <v>7.020767952781171e-05</v>
+      </c>
+      <c r="EO14" t="n">
+        <v>9.275021147914231e-05</v>
+      </c>
+      <c r="EP14" t="n">
+        <v>0.0001407688832841814</v>
+      </c>
+      <c r="EQ14" t="n">
+        <v>0.0002346533583477139</v>
+      </c>
+      <c r="ER14" t="n">
+        <v>0.0001885856036096811</v>
+      </c>
+      <c r="ES14" t="n">
+        <v>4.690166679210961e-05</v>
+      </c>
+      <c r="ET14" t="n">
+        <v>0.0002865936257876456</v>
+      </c>
+      <c r="EU14" t="n">
+        <v>0.0001435314770787954</v>
+      </c>
+      <c r="EV14" t="n">
+        <v>4.41088923253119e-05</v>
+      </c>
+      <c r="EW14" t="n">
+        <v>0.0001933383318828419</v>
+      </c>
+      <c r="EX14" t="n">
+        <v>0.0001000548800220713</v>
+      </c>
+      <c r="EY14" t="n">
+        <v>0.0003833250957541168</v>
+      </c>
+      <c r="EZ14" t="n">
+        <v>6.90052775098593e-06</v>
+      </c>
+      <c r="FA14" t="n">
+        <v>0.0002668059314601123</v>
+      </c>
+      <c r="FB14" t="n">
+        <v>8.830708975438029e-05</v>
+      </c>
+      <c r="FC14" t="n">
+        <v>0.0002844936971087009</v>
+      </c>
+      <c r="FD14" t="n">
+        <v>9.522432810626924e-05</v>
+      </c>
+      <c r="FE14" t="n">
+        <v>1.904139207908884e-05</v>
+      </c>
+      <c r="FF14" t="n">
+        <v>1.111279743781779e-05</v>
+      </c>
+      <c r="FG14" t="n">
+        <v>6.440480501623824e-05</v>
+      </c>
+      <c r="FH14" t="n">
+        <v>0.0003995001025032252</v>
+      </c>
+      <c r="FI14" t="n">
+        <v>0.0003408267511986196</v>
+      </c>
+      <c r="FJ14" t="n">
+        <v>0.00018006467144005</v>
+      </c>
+      <c r="FK14" t="n">
+        <v>0.0002227339427918196</v>
+      </c>
+      <c r="FL14" t="n">
+        <v>0.0001949848083313555</v>
+      </c>
+      <c r="FM14" t="n">
+        <v>0.0001910381542984396</v>
+      </c>
+      <c r="FN14" t="n">
+        <v>0.0002873990160878748</v>
+      </c>
+      <c r="FO14" t="n">
+        <v>0.0003788147587329149</v>
+      </c>
+      <c r="FP14" t="n">
+        <v>0.0002070073969662189</v>
+      </c>
+      <c r="FQ14" t="n">
+        <v>9.174937440548092e-05</v>
+      </c>
+      <c r="FR14" t="n">
+        <v>0.000688027183059603</v>
+      </c>
+      <c r="FS14" t="n">
+        <v>0.0002368695859331638</v>
+      </c>
+      <c r="FT14" t="n">
+        <v>0.0004886646056547761</v>
+      </c>
+      <c r="FU14" t="n">
+        <v>8.836537745082751e-05</v>
+      </c>
+      <c r="FV14" t="n">
+        <v>4.512577288551256e-05</v>
+      </c>
+      <c r="FW14" t="n">
+        <v>0.000255766324698925</v>
+      </c>
+      <c r="FX14" t="n">
+        <v>0.0001814593269955367</v>
+      </c>
+      <c r="FY14" t="n">
+        <v>2.986157414852642e-05</v>
+      </c>
+      <c r="FZ14" t="n">
+        <v>0.0003890835214406252</v>
+      </c>
+      <c r="GA14" t="n">
+        <v>0.0003890349180437624</v>
+      </c>
+      <c r="GB14" t="n">
+        <v>9.078110451810062e-05</v>
+      </c>
+      <c r="GC14" t="n">
+        <v>0.0005445434362627566</v>
+      </c>
+      <c r="GD14" t="n">
+        <v>0.0004597895313054323</v>
+      </c>
+      <c r="GE14" t="n">
+        <v>7.007413660176098e-05</v>
+      </c>
+      <c r="GF14" t="n">
+        <v>0.0001750827650539577</v>
+      </c>
+      <c r="GG14" t="n">
+        <v>0.000151219210238196</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>0</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER15" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES15" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>0</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG16" t="n">
         <v>0</v>
       </c>
     </row>
